--- a/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2059,6 +2063,6862 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0029296875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0009726418028326389</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0009558318314951775</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.280491932446589e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0008651022344448264</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.001078689412773253</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002431604507081597</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0002389579578737944</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.820122983111647e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0002162755586112066</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0002696723531933133</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(31.743), 'mean_duration_us': np.float64(3.1742999999999997), 'median_duration_us': np.float64(3.216), 'std_dev_duration_us': np.float64(0.22374005005809758), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '2', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.174267578125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.2159423828125</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2358569953110188</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.847900390625</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.551025390625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>31.74267578125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3981312</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.61185101736415</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.605380788344162</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02189358768515036</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.595095422115714</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.647883796281326</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8059253062550091</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.80269019255759</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.01094679109303155</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7975475107350711</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8239416911883589</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(24.704), 'mean_duration_us': np.float64(4.9408), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.05935115837117255), 'min_duration_us': np.float64(4.832), 'max_duration_us': np.float64(4.992)}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[3981312, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.940771484375</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.9599609375</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06632016155483225</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.83203125</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.991943359375</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24.703857421875</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0004849575764314781</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0004954890671700488</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.789683268713756e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000440935675789179</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0005224021892362551</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0002421634711959526</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.000247422369042001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.892377601022212e-05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0002201811436970673</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0002608614312961274</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(15.936), 'mean_duration_us': np.float64(3.1872), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.2268165778773677), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.488)}]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[[1, 1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[768, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.187255859375</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.10400390625</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2535787377464963</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.944091796875</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.488037109375</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>15.936279296875</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5.184e-06</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03955078125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>vector_fp32</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>['float', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[5184, 1, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>['', '-1', 'False']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23754</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('int', None)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>[[1], [1]]</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>['int', 'int']</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>[[2], [2]]</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23812</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>262422.467</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2186.853891666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2146.764</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2395.817</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47.58757680193121</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24.33694659741849</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>130015.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1083.464166666667</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1075.574</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1096.694</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.57699087253397</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12.0576000366843</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99311.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" t="n">
+        <v>827.5950833333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>825.432</v>
+      </c>
+      <c r="I4" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.00908818787638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.210097402538072</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25101.542</v>
+      </c>
+      <c r="F5" t="n">
+        <v>740</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33.9210027027027</v>
+      </c>
+      <c r="H5" t="n">
+        <v>19.936</v>
+      </c>
+      <c r="I5" t="n">
+        <v>65.95099999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.551902782668002</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.327906197021071</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7532.958</v>
+      </c>
+      <c r="F6" t="n">
+        <v>720</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.46244166666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.384</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.366023349558413</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.698603281427868</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5327.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>190</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.03847368421053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44.704</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9660520940560176</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4940524356014591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4802.707</v>
+      </c>
+      <c r="F8" t="n">
+        <v>360</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.34085277777778</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31.711</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8709208126592021</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4454009792616117</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4242.816</v>
+      </c>
+      <c r="F9" t="n">
+        <v>385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.0203012987013</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.328</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.807</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7693904205864452</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3934769289958421</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4102.415</v>
+      </c>
+      <c r="F10" t="n">
+        <v>185</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22.17521621621622</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="I10" t="n">
+        <v>34.272</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7439301638982557</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3804562007087929</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2512.972</v>
+      </c>
+      <c r="F11" t="n">
+        <v>375</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.701258666666666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.849</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4557012569015391</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.233051941260837</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2388.192</v>
+      </c>
+      <c r="F12" t="n">
+        <v>360</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.633866666666667</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4330737056052357</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.221479897787799</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>982.966</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>196.5932</v>
+      </c>
+      <c r="H13" t="n">
+        <v>195.966</v>
+      </c>
+      <c r="I13" t="n">
+        <v>197.245</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1782506298086403</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.09115984360088371</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>287.137</v>
+      </c>
+      <c r="F14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.392808333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.913</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.05206929953972318</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02662896174641538</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>280.51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28.051</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.424</v>
+      </c>
+      <c r="I15" t="n">
+        <v>44.768</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.05086756222252008</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.026014376619826</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>219.806</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.96120000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>43.551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>44.799</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.03985952508603347</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02038471379736008</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>195.071</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.0142</v>
+      </c>
+      <c r="H17" t="n">
+        <v>38.624</v>
+      </c>
+      <c r="I17" t="n">
+        <v>39.231</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.03537409087130304</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01809080054759573</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>185.697</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.09495</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.03367421376077613</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01722145982379177</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>176.768</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.838400000000002</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.992000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.03205503275801373</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0163933882083826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>167.428</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.790466666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.03036132119279916</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.01552720062993914</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.339166666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.025451008370221</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.01301599856900852</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>115.748</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.929133333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.02098969231803592</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0107344196819779</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>98.878</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.9439</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.616</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.01793049380570511</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.009169903145752934</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86.78200000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17.3564</v>
+      </c>
+      <c r="H24" t="n">
+        <v>17.215</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17.408</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.01573701039105465</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.008048125313970056</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>83.104</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.540266666666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.152</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.01507004345991341</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.007707029177619409</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>72.383</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.61915</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.992</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.01312590195127686</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.006712768253797959</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>65.407</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.0814</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.184</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.01186087712483823</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.006065817017478733</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>56.543</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11.3086</v>
+      </c>
+      <c r="H28" t="n">
+        <v>11.168</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.01025348319399648</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.005243773474082285</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>54.623</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.462300000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.088</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.888</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.009905311223417044</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.005065713500783416</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.759</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.008767768113289531</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.004483958181771015</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36.702</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.6702</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.006655524825107597</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.003403727677091205</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>35.168</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.344533333333333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.006377349927780066</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.003261465177590963</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>24.095</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.606333333333333</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.004369376891203955</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.002234559925331388</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>23.615</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.831</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.004282333898559094</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.00219004493200667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>22.176</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.4352</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.832</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.004021386260192526</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.002056592691601945</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22.144</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.428800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.608</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.004015583394016202</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.002053625025380297</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18.527</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.7054</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.488</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.871</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.003359678176523581</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.001718186002764666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14.657</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.9314</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.976</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.002657894048324398</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.001359283869084131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>13.985</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.816</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.002536033858621594</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.001296962878429527</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.002408189463174456</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.001231581481983848</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>13.183</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.6366</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.527</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.002390599525077474</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.001222585743749479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12.223</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.4446</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.624</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.002216513539787754</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.001133555757100044</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.687</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.1374</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.001937975963324203</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.000991107778460948</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.143</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.001839327238326695</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.000940657452692935</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.0096</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.856</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.001822099979365733</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.0009318471935974179</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9.247</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.8494</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.001676846985389623</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.0008575627984867958</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8.769</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.7538</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.001590166671880784</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0008132332843009313</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.001566773867607478</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.0008012698798449135</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8.478999999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.001537578197157847</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.0007863388091672478</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.446999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.6894</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.001531775330981523</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.0007833711429456</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.5488</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.001404293614670406</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.0007181752256387743</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.454000000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.00135170513994747</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.0006912807505050909</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.134</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.00129367647818423</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.0006616040882886126</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.001276630558791278</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0006528865687625221</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7.009</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.4018</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.001271009032182964</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.0006500116421103007</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.001270827692614954</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.984</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.1968</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.001085135974972586</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.0005549535834481437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.20864</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.20864</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.29728</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.29728</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.38592</v>
+      </c>
+      <c r="C4" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.38592</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.47456</v>
+      </c>
+      <c r="C5" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.47456</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5632</v>
+      </c>
+      <c r="C6" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.5632</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.65184</v>
+      </c>
+      <c r="C7" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.65184</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.74048</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.74048</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.82912</v>
+      </c>
+      <c r="C9" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.82912</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.91776</v>
+      </c>
+      <c r="C10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1.91776</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.0064</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.0064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.09504</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.09504</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.18368</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.18368</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.272320000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.272320000000001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.36096</v>
+      </c>
+      <c r="C15" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.36096</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.4496</v>
+      </c>
+      <c r="C16" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.4496</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2.53824</v>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.53824</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.62688</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.62688</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.715520000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.715520000000001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.80416</v>
+      </c>
+      <c r="C20" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2.80416</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.8928</v>
+      </c>
+      <c r="C21" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.8928</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2.98144</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2.98144</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.07008</v>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3.07008</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.15872</v>
+      </c>
+      <c r="C24" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.15872</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.24736</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.24736</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.424640000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3.424640000000001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.51328</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.51328</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.60192</v>
+      </c>
+      <c r="C29" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3.60192</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.690560000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.690560000000001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.7792</v>
+      </c>
+      <c r="C31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3.7792</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.867840000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3.867840000000001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.95648</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3.95648</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4.045120000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4.045120000000001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4.133760000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4.133760000000001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.2224</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4.2224</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.31104</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.31104</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.39968</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.39968</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.48832</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.48832</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.576960000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.576960000000001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.6656</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.6656</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.754240000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.754240000000001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.842880000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.842880000000001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.931520000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.931520000000001</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5.020160000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.020160000000001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5.1088</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.1088</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5.19744</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.19744</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5.286080000000001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.286080000000001</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5.374720000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5.374720000000001</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5.463360000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.463360000000001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5.64064</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5.64064</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5.729280000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5.729280000000001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5.817920000000001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5.817920000000001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5.906560000000001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.906560000000001</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.995200000000001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5.995200000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6.08384</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6.08384</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6.172480000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6.172480000000001</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6.261120000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6.261120000000001</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6.349760000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6.349760000000001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>6.438400000000001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6.438400000000001</v>
+      </c>
+      <c r="B62" t="n">
+        <v>6.52704</v>
+      </c>
+      <c r="C62" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6.52704</v>
+      </c>
+      <c r="B63" t="n">
+        <v>6.615680000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6.615680000000001</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6.704320000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6.704320000000001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6.792960000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6.792960000000001</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6.881600000000001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6.881600000000001</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6.97024</v>
+      </c>
+      <c r="C67" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6.97024</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.058880000000001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7.058880000000001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.147520000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7.147520000000001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.236160000000001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7.236160000000001</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.324800000000001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7.324800000000001</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.41344</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7.41344</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.502080000000001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7.502080000000001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7.590720000000001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7.590720000000001</v>
+      </c>
+      <c r="B75" t="n">
+        <v>7.679360000000001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7.679360000000001</v>
+      </c>
+      <c r="B76" t="n">
+        <v>7.768000000000001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>7.768000000000001</v>
+      </c>
+      <c r="B77" t="n">
+        <v>7.856640000000001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7.856640000000001</v>
+      </c>
+      <c r="B78" t="n">
+        <v>7.945280000000001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7.945280000000001</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8.033920000000002</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8.033920000000002</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8.12256</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8.12256</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8.211200000000002</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8.211200000000002</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8.29984</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8.29984</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8.388480000000001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8.388480000000001</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8.477120000000001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8.477120000000001</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8.565760000000001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8.565760000000001</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8.654400000000001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8.654400000000001</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8.743040000000001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8.743040000000001</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8.831680000000002</v>
+      </c>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8.831680000000002</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8.92032</v>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8.92032</v>
+      </c>
+      <c r="B90" t="n">
+        <v>9.008960000000002</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9.008960000000002</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9.0976</v>
+      </c>
+      <c r="C91" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>9.0976</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9.186240000000002</v>
+      </c>
+      <c r="C92" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9.186240000000002</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9.27488</v>
+      </c>
+      <c r="C93" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9.27488</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9.363520000000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>9.363520000000001</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9.452160000000003</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9.452160000000003</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9.540800000000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9.540800000000001</v>
+      </c>
+      <c r="B97" t="n">
+        <v>9.629440000000002</v>
+      </c>
+      <c r="C97" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9.629440000000002</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.71808</v>
+      </c>
+      <c r="C98" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9.71808</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9.806720000000002</v>
+      </c>
+      <c r="C99" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.806720000000002</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.89536</v>
+      </c>
+      <c r="C100" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9.89536</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9.984</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), (1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), (5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2174.634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>231</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.414</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2016746208202157</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((768,), (5, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1579.851</v>
+      </c>
+      <c r="G3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.5827125</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1465147014980169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>934.809</v>
+      </c>
+      <c r="G4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.790075</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.086693784156012</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 64), (1, 12, 5, 64), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((3840, 320, 64, 1), (3840, 64, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>457.92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04246730363178042</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>451.141</v>
+      </c>
+      <c r="G6" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.609128</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04183862209063821</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((3072,), (5, 768), (768, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>422.845</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.047416666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.03921446323414612</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>385.496</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.424933333333333</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.03575073305563597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((300, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>287.137</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.392808333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02662896174641538</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>187.747</v>
+      </c>
+      <c r="G10" t="n">
+        <v>125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.501976</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01741157594111608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((12, 5, 64), (12, 64, 5))</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((320, 64, 1), (320, 1, 64))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>185.697</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.09495</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01722145982379177</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>((5308416, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>176.768</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.838400000000002</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0163933882083826</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (12, 5, 64))</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (320, 64, 1))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>167.428</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.790466666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01552720062993914</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>((1, 5, 12, 64), (1, 5, 12, 64), ())</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>((3840, 768, 64, 1), (3840, 64, 320, 1), ())</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>163.172</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.719533333333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01513250102245998</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.339166666666666</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01301599856900852</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>115.748</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.929133333333333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0107344196819779</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072),)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1),)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>105.021</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.75035</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.009739602320739891</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>94.07900000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.567983333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.008724845952075188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), (1, 5, 3072))</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), (15360, 3072, 1))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>89.14700000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.485783333333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.008267454395663716</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>86.495</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.441583333333333</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.008021509057544653</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>83.104</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.540266666666667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.007707029177619409</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>((1, 3, 1008, 1008), (1024, 3, 14, 14), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>((3048192, 1016064, 1008, 1), (588, 196, 14, 1), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('', '', '[0, 0]', '[14, 14]', '[1, 1]', '1', 'False', 'False', 'True')</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.004483958181771015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>35.168</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.344533333333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.003261465177590963</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>((1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('', '2', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>31.743</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.1743</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.002943832152305219</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>((49408, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.632</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.002611546275050088</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>((1, 768), (1, 1))</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>26.687</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.6687</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.002474940889284862</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>((16, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>26.463</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.2926</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.002454167225733327</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>24.704</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.9408</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.002291038323112123</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 768, 1))</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (768, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>23.615</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.00219004493200667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>22.176</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.4352</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.002056592691601945</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4), (5184, 4), ())</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1), (4, 1), ())</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>22.144</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.428800000000001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.002053625025380297</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>((1, 1024), (), (1024,), (1024,), ())</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>((5309440, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('', '[1024]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>20.128</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.0256</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.001866662053416484</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 768))</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>18.784</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7568</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.001742020072107275</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>((1, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>((5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>18.527</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.7054</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.001718186002764666</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>((1, 1024), (1024, 768))</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>((1024, 1), (1, 1024))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>17.918</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.5836</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.00166170760498393</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>15.936</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.1872</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.001477897778380618</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>15.296</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.5296</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.001418544453947662</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('', '', '')</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>14.657</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.9314</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.001359283869084131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.912</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.001350288130849762</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>13.985</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.001296962878429527</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 1))</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>13.183</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.6366</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.001222585743749479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>12.223</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.4446</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.001133555757100044</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>((5,), (5, 1))</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>((1,), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>10.687</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.1374</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.000991107778460948</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 1))</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10.143</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.000940657452692935</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.0096</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0009318471935974179</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9.247</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.8494</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0008575627984867958</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4),)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1),)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>8.896000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.7792</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.0008250112096180963</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8.798999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.7598</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0008160154713837261</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8.769</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.7538</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.0008132332843009313</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>((1, 5), (1, 5), ())</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0008012698798449135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>('', '1.', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>8.478999999999999</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.0007863388091672478</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8.446999999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.6894</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0007833711429456</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7.872</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.5744</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0007300458905253656</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>((5,), (), ())</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>((1,), (), ())</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.5488</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.0007181752256387743</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>('', '', '0')</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>7.454000000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.0006912807505050909</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>7.425</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.0006885913029917225</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>('', '', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>7.134</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0006616040882886126</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>('0', '5', '1', '')</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>7.104</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.4208</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0006588219012058177</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>((), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>((), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0006528865687625221</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>7.009</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.4018</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.0006500116421103007</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>((5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>('0', '1', '1', '')</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.2352</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.0005727595807780308</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5.984</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.1968</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.0005549535834481437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20397,7 +27257,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20441,28 +27301,46 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="K46" t="n">
         <v>10</v>
       </c>
       <c r="L46" t="n">
-        <v>173.092</v>
+        <v>207.634</v>
       </c>
       <c r="M46" t="n">
-        <v>17.3092</v>
+        <v>20.7634</v>
       </c>
       <c r="N46" t="n">
-        <v>7.994499745311009</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+        <v>10.99204100146</v>
+      </c>
+      <c r="O46" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.0029296875</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0.0009726418028326389</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7.280491932446589e-05</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.0002431604507081597</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.820122983111647e-05</v>
+      </c>
       <c r="W46" t="n">
         <v>3.174267578125</v>
       </c>
@@ -20473,20 +27351,32 @@
         <v>31.74267578125</v>
       </c>
       <c r="Z46" t="n">
-        <v>17.22</v>
+        <v>19.61</v>
       </c>
       <c r="AA46" t="n">
-        <v>9.619999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="AB46" t="n">
-        <v>25.261</v>
-      </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
+        <v>38.951</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.0009558318314951775</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.0008651022344448264</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.001078689412773253</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.0002389579578737944</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.0002162755586112066</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.0002696723531933133</v>
+      </c>
       <c r="AI46" t="n">
         <v>3.2159423828125</v>
       </c>
@@ -20506,9 +27396,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 768, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP46" t="n">
         <v>0.005600731403536479</v>
@@ -20923,7 +27817,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -20953,7 +27847,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -20963,32 +27857,50 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4578</v>
+        <v>4577</v>
       </c>
       <c r="K50" t="n">
         <v>5</v>
       </c>
       <c r="L50" t="n">
-        <v>85.33199999999999</v>
+        <v>93.05199999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>17.0664</v>
+        <v>18.6104</v>
       </c>
       <c r="N50" t="n">
-        <v>1.155311343318327</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+        <v>1.133556482933252</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="P50" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>1.61185101736415</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.02189358768515036</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.8059253062550091</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.01094679109303155</v>
+      </c>
       <c r="W50" t="n">
         <v>4.940771484375</v>
       </c>
@@ -20999,20 +27911,32 @@
         <v>24.703857421875</v>
       </c>
       <c r="Z50" t="n">
-        <v>16.78</v>
+        <v>18.39</v>
       </c>
       <c r="AA50" t="n">
-        <v>16</v>
+        <v>17.51</v>
       </c>
       <c r="AB50" t="n">
-        <v>18.941</v>
-      </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
+        <v>20.431</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.605380788344162</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.595095422115714</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.647883796281326</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.80269019255759</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.7975475107350711</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.8239416911883589</v>
+      </c>
       <c r="AI50" t="n">
         <v>4.9599609375</v>
       </c>
@@ -21032,9 +27956,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 3981312, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP50" t="n">
         <v>0.004358790386943698</v>
@@ -22530,7 +29458,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -22560,7 +29488,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -22570,32 +29498,50 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>4582</v>
+        <v>4581</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>51.332</v>
+        <v>56.662</v>
       </c>
       <c r="M61" t="n">
-        <v>10.2664</v>
+        <v>11.3324</v>
       </c>
       <c r="N61" t="n">
-        <v>0.2338146701984292</v>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+        <v>0.3035264403639328</v>
+      </c>
+      <c r="O61" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>0.0004849575764314781</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.789683268713756e-05</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.0002421634711959526</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.892377601022212e-05</v>
+      </c>
       <c r="W61" t="n">
         <v>3.187255859375</v>
       </c>
@@ -22606,20 +29552,32 @@
         <v>15.936279296875</v>
       </c>
       <c r="Z61" t="n">
-        <v>10.21</v>
+        <v>11.211</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.091</v>
+        <v>11.071</v>
       </c>
       <c r="AB61" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
+        <v>11.85</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.0004954890671700488</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.000440935675789179</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.0005224021892362551</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0.000247422369042001</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.0002201811436970673</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0.0002608614312961274</v>
+      </c>
       <c r="AI61" t="n">
         <v>3.10400390625</v>
       </c>
@@ -22639,9 +29597,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP61" t="n">
         <v>0.002811824073327106</v>

--- a/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -2069,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2284,34 +2284,34 @@
         <v>7.68e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0029296875</v>
+        <v>0.001466751098632812</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.4993498049414825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009726418028326389</v>
+        <v>0.0004862886133149629</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009558318314951775</v>
+        <v>0.0004904358115998443</v>
       </c>
       <c r="K2" t="n">
-        <v>7.280491932446589e-05</v>
+        <v>3.557215699598599e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008651022344448264</v>
+        <v>0.0004331143348229632</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001078689412773253</v>
+        <v>0.0005400469781397342</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002431604507081597</v>
+        <v>0.0002428281242040907</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002389579578737944</v>
+        <v>0.0002448990268586999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.820122983111647e-05</v>
+        <v>1.77629496572934e-05</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0002162755586112066</v>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(31.743), 'mean_duration_us': np.float64(3.1742999999999997), 'median_duration_us': np.float64(3.216), 'std_dev_duration_us': np.float64(0.22374005005809758), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(47.679), 'mean_duration_us': np.float64(3.1786000000000003), 'median_duration_us': np.float64(3.136), 'std_dev_duration_us': np.float64(0.22485248497626176), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.18)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>3.174267578125</v>
+        <v>3.178597005208333</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.2159423828125</v>
+        <v>3.135986328125</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2358569953110188</v>
+        <v>0.2327518180455004</v>
       </c>
       <c r="AF2" t="n">
         <v>2.847900390625</v>
@@ -2385,10 +2385,10 @@
         <v>3.551025390625</v>
       </c>
       <c r="AH2" t="n">
-        <v>31.74267578125</v>
+        <v>47.678955078125</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>4506</v>
@@ -2537,12 +2537,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::linalg_norm</t>
+          <t>aten::max</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2552,53 +2552,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>('float', None)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>norm</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.68e-07</v>
+        <v>5.184e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001466751098632812</v>
+        <v>0.01977920532226562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4993498049414825</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0004849575764314781</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0004954890671700488</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.789683268713756e-05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.000440935675789179</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0005224021892362551</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0002421634711959526</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.000247422369042001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.892377601022212e-05</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0002201811436970673</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0002608614312961274</v>
-      </c>
+        <v>0.2499517839922854</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>python3</t>
@@ -2616,62 +2596,58 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(15.936), 'mean_duration_us': np.float64(3.1872), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.2268165778773677), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.488)}]</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[[1, 1, 768], [], [], [], []]</t>
+          <t>[[1, 5184, 1], [], []]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+          <t>['float', 'Scalar', 'Scalar']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[768, 768, 1], [], [], [], []]</t>
+          <t>[[5184, 1, 1], [], []]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['', '', '[-1]', 'True', '']</t>
+          <t>['', '-1', 'False']</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>3.187255859375</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.10400390625</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2535787377464963</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.944091796875</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.488037109375</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.936279296875</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4581</v>
+        <v>23754</v>
       </c>
     </row>
     <row r="5">
@@ -2682,17 +2658,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('float', None)</t>
+          <t>('int', None)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2701,14 +2677,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.184e-06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.03955078125</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.125</v>
-      </c>
+        <v>1e-09</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -2734,11 +2706,7 @@
           <t>thread 21587 (python3)</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>vector_fp32</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2747,22 +2715,22 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[[1, 5184, 1], [], []]</t>
+          <t>[[1], [1]]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>['float', 'Scalar', 'Scalar']</t>
+          <t>['int', 'int']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[5184, 1, 1], [], []]</t>
+          <t>[[2], [2]]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['', '-1', 'False']</t>
+          <t>['', '']</t>
         </is>
       </c>
       <c r="AC5" t="n">
@@ -2787,114 +2755,6 @@
         <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23754</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>aten::max</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>('int', None)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1e-09</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>thread 21587 (python3)</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>[[1], [1]]</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>['int', 'int']</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>[[2], [2]]</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ6" t="n">
         <v>23812</v>
       </c>
     </row>
@@ -27319,10 +27179,10 @@
         <v>7.68e-07</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0029296875</v>
+        <v>0.001466751098632812</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.25</v>
+        <v>0.4993498049414825</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -27330,10 +27190,10 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>0.0009726418028326389</v>
+        <v>0.0004869541317567053</v>
       </c>
       <c r="T46" t="n">
-        <v>7.280491932446589e-05</v>
+        <v>3.644985869825148e-05</v>
       </c>
       <c r="U46" t="n">
         <v>0.0002431604507081597</v>
@@ -27360,13 +27220,13 @@
         <v>38.951</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.0009558318314951775</v>
+        <v>0.0004785382020962185</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.0008651022344448264</v>
+        <v>0.0004331143348229632</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.001078689412773253</v>
+        <v>0.0005400469781397342</v>
       </c>
       <c r="AF46" t="n">
         <v>0.0002389579578737944</v>
@@ -27398,7 +27258,7 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>{'num_input_elems': 768, 'num_output_elems': 768, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
         </is>
       </c>
       <c r="AO46" t="b">

--- a/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2059,6 +2063,6722 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0004862886133149629</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0004904358115998443</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.557215699598599e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0004331143348229632</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0005400469781397342</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002428281242040907</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0002448990268586999</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.77629496572934e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0002162755586112066</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0002696723531933133</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(47.679), 'mean_duration_us': np.float64(3.1786000000000003), 'median_duration_us': np.float64(3.136), 'std_dev_duration_us': np.float64(0.22485248497626176), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.18)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '2', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.178597005208333</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.135986328125</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2327518180455004</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.847900390625</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.551025390625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>47.678955078125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3981312</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.61185101736415</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.605380788344162</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02189358768515036</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.595095422115714</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.647883796281326</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8059253062550091</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.80269019255759</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.01094679109303155</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7975475107350711</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8239416911883589</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(24.704), 'mean_duration_us': np.float64(4.9408), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.05935115837117255), 'min_duration_us': np.float64(4.832), 'max_duration_us': np.float64(4.992)}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[3981312, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.940771484375</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.9599609375</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06632016155483225</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.83203125</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.991943359375</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24.703857421875</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5.184e-06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01977920532226562</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2499517839922854</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>vector_fp32</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>['float', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[5184, 1, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>['', '-1', 'False']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23754</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('int', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>thread 21587 (python3)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>[[1], [1]]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>['int', 'int']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[2], [2]]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23812</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>262422.467</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2186.853891666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2146.764</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2395.817</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47.58757680193121</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24.33694659741849</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>130015.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1083.464166666667</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1075.574</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1096.694</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.57699087253397</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12.0576000366843</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99311.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" t="n">
+        <v>827.5950833333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>825.432</v>
+      </c>
+      <c r="I4" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.00908818787638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.210097402538072</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25101.542</v>
+      </c>
+      <c r="F5" t="n">
+        <v>740</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33.9210027027027</v>
+      </c>
+      <c r="H5" t="n">
+        <v>19.936</v>
+      </c>
+      <c r="I5" t="n">
+        <v>65.95099999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.551902782668002</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.327906197021071</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7532.958</v>
+      </c>
+      <c r="F6" t="n">
+        <v>720</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.46244166666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.384</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.366023349558413</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.698603281427868</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5327.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>190</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.03847368421053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44.704</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9660520940560176</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4940524356014591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4802.707</v>
+      </c>
+      <c r="F8" t="n">
+        <v>360</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.34085277777778</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31.711</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8709208126592021</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4454009792616117</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4242.816</v>
+      </c>
+      <c r="F9" t="n">
+        <v>385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.0203012987013</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.328</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.807</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7693904205864452</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3934769289958421</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4102.415</v>
+      </c>
+      <c r="F10" t="n">
+        <v>185</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22.17521621621622</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="I10" t="n">
+        <v>34.272</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7439301638982557</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3804562007087929</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2512.972</v>
+      </c>
+      <c r="F11" t="n">
+        <v>375</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.701258666666666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.849</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4557012569015391</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.233051941260837</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2388.192</v>
+      </c>
+      <c r="F12" t="n">
+        <v>360</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.633866666666667</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4330737056052357</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.221479897787799</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>982.966</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>196.5932</v>
+      </c>
+      <c r="H13" t="n">
+        <v>195.966</v>
+      </c>
+      <c r="I13" t="n">
+        <v>197.245</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1782506298086403</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.09115984360088371</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>287.137</v>
+      </c>
+      <c r="F14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.392808333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.913</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.05206929953972318</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02662896174641538</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>280.51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28.051</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.424</v>
+      </c>
+      <c r="I15" t="n">
+        <v>44.768</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.05086756222252008</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.026014376619826</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>219.806</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.96120000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>43.551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>44.799</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.03985952508603347</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02038471379736008</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>195.071</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.0142</v>
+      </c>
+      <c r="H17" t="n">
+        <v>38.624</v>
+      </c>
+      <c r="I17" t="n">
+        <v>39.231</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.03537409087130304</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01809080054759573</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>185.697</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.09495</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.03367421376077613</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01722145982379177</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>176.768</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.838400000000002</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.992000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.03205503275801373</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0163933882083826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>167.428</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.790466666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.03036132119279916</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.01552720062993914</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.339166666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.025451008370221</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.01301599856900852</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>115.748</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.929133333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.02098969231803592</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0107344196819779</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>98.878</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.9439</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.616</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.01793049380570511</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.009169903145752934</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86.78200000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17.3564</v>
+      </c>
+      <c r="H24" t="n">
+        <v>17.215</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17.408</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.01573701039105465</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.008048125313970056</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>83.104</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.540266666666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.152</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.01507004345991341</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.007707029177619409</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>72.383</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.61915</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.992</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.01312590195127686</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.006712768253797959</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>65.407</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.0814</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.184</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.01186087712483823</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.006065817017478733</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>56.543</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11.3086</v>
+      </c>
+      <c r="H28" t="n">
+        <v>11.168</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.01025348319399648</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.005243773474082285</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>54.623</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.462300000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.088</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.888</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.009905311223417044</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.005065713500783416</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.759</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.008767768113289531</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.004483958181771015</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36.702</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.6702</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.006655524825107597</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.003403727677091205</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>35.168</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.344533333333333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.006377349927780066</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.003261465177590963</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>24.095</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.606333333333333</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.004369376891203955</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.002234559925331388</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>23.615</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.831</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.004282333898559094</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.00219004493200667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>22.176</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.4352</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.832</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.004021386260192526</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.002056592691601945</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22.144</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.428800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.608</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.004015583394016202</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.002053625025380297</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18.527</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.7054</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.488</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.871</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.003359678176523581</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.001718186002764666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14.657</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.9314</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.976</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.002657894048324398</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.001359283869084131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>13.985</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.816</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.002536033858621594</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.001296962878429527</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.002408189463174456</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.001231581481983848</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>13.183</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.6366</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.527</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.002390599525077474</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.001222585743749479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12.223</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.4446</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.624</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.002216513539787754</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.001133555757100044</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.687</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.1374</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.001937975963324203</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.000991107778460948</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.143</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.001839327238326695</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.000940657452692935</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.0096</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.856</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.001822099979365733</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.0009318471935974179</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9.247</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.8494</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.001676846985389623</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.0008575627984867958</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8.769</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.7538</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.001590166671880784</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0008132332843009313</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.001566773867607478</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.0008012698798449135</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8.478999999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.001537578197157847</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.0007863388091672478</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.446999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.6894</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.001531775330981523</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.0007833711429456</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.5488</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.001404293614670406</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.0007181752256387743</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.454000000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.00135170513994747</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.0006912807505050909</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.134</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.00129367647818423</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.0006616040882886126</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.001276630558791278</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0006528865687625221</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7.009</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.4018</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.001271009032182964</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.0006500116421103007</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.001270827692614954</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.984</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.1968</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.001085135974972586</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.0005549535834481437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.20864</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.20864</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.29728</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.29728</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.38592</v>
+      </c>
+      <c r="C4" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.38592</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.47456</v>
+      </c>
+      <c r="C5" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.47456</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5632</v>
+      </c>
+      <c r="C6" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.5632</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.65184</v>
+      </c>
+      <c r="C7" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.65184</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.74048</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.74048</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.82912</v>
+      </c>
+      <c r="C9" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.82912</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.91776</v>
+      </c>
+      <c r="C10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1.91776</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.0064</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.0064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.09504</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.09504</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.18368</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.18368</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.272320000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.272320000000001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.36096</v>
+      </c>
+      <c r="C15" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.36096</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.4496</v>
+      </c>
+      <c r="C16" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.4496</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2.53824</v>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.53824</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.62688</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.62688</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.715520000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.715520000000001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.80416</v>
+      </c>
+      <c r="C20" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2.80416</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.8928</v>
+      </c>
+      <c r="C21" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.8928</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2.98144</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2.98144</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.07008</v>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3.07008</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.15872</v>
+      </c>
+      <c r="C24" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.15872</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.24736</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.24736</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.424640000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3.424640000000001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.51328</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.51328</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.60192</v>
+      </c>
+      <c r="C29" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3.60192</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.690560000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.690560000000001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.7792</v>
+      </c>
+      <c r="C31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3.7792</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.867840000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3.867840000000001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.95648</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3.95648</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4.045120000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4.045120000000001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4.133760000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4.133760000000001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.2224</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4.2224</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.31104</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.31104</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.39968</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.39968</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.48832</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.48832</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.576960000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.576960000000001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.6656</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.6656</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.754240000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.754240000000001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.842880000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.842880000000001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.931520000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.931520000000001</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5.020160000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.020160000000001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5.1088</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.1088</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5.19744</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.19744</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5.286080000000001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.286080000000001</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5.374720000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5.374720000000001</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5.463360000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.463360000000001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5.64064</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5.64064</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5.729280000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5.729280000000001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5.817920000000001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5.817920000000001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5.906560000000001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.906560000000001</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.995200000000001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5.995200000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6.08384</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6.08384</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6.172480000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6.172480000000001</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6.261120000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6.261120000000001</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6.349760000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6.349760000000001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>6.438400000000001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6.438400000000001</v>
+      </c>
+      <c r="B62" t="n">
+        <v>6.52704</v>
+      </c>
+      <c r="C62" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6.52704</v>
+      </c>
+      <c r="B63" t="n">
+        <v>6.615680000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6.615680000000001</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6.704320000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6.704320000000001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6.792960000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6.792960000000001</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6.881600000000001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6.881600000000001</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6.97024</v>
+      </c>
+      <c r="C67" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6.97024</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.058880000000001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7.058880000000001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.147520000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7.147520000000001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.236160000000001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7.236160000000001</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.324800000000001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7.324800000000001</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.41344</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7.41344</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.502080000000001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7.502080000000001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7.590720000000001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7.590720000000001</v>
+      </c>
+      <c r="B75" t="n">
+        <v>7.679360000000001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7.679360000000001</v>
+      </c>
+      <c r="B76" t="n">
+        <v>7.768000000000001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>7.768000000000001</v>
+      </c>
+      <c r="B77" t="n">
+        <v>7.856640000000001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7.856640000000001</v>
+      </c>
+      <c r="B78" t="n">
+        <v>7.945280000000001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7.945280000000001</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8.033920000000002</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8.033920000000002</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8.12256</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8.12256</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8.211200000000002</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8.211200000000002</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8.29984</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8.29984</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8.388480000000001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8.388480000000001</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8.477120000000001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8.477120000000001</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8.565760000000001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8.565760000000001</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8.654400000000001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8.654400000000001</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8.743040000000001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8.743040000000001</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8.831680000000002</v>
+      </c>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8.831680000000002</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8.92032</v>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8.92032</v>
+      </c>
+      <c r="B90" t="n">
+        <v>9.008960000000002</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9.008960000000002</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9.0976</v>
+      </c>
+      <c r="C91" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>9.0976</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9.186240000000002</v>
+      </c>
+      <c r="C92" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9.186240000000002</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9.27488</v>
+      </c>
+      <c r="C93" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9.27488</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9.363520000000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>9.363520000000001</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9.452160000000003</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9.452160000000003</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9.540800000000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9.540800000000001</v>
+      </c>
+      <c r="B97" t="n">
+        <v>9.629440000000002</v>
+      </c>
+      <c r="C97" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9.629440000000002</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.71808</v>
+      </c>
+      <c r="C98" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9.71808</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9.806720000000002</v>
+      </c>
+      <c r="C99" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.806720000000002</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.89536</v>
+      </c>
+      <c r="C100" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9.89536</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9.984</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), (1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), (5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2174.634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>231</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.414</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2016746208202157</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((768,), (5, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1579.851</v>
+      </c>
+      <c r="G3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.5827125</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1465147014980169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>934.809</v>
+      </c>
+      <c r="G4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.790075</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.086693784156012</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 64), (1, 12, 5, 64), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((3840, 320, 64, 1), (3840, 64, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>457.92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04246730363178042</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>451.141</v>
+      </c>
+      <c r="G6" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.609128</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04183862209063821</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((3072,), (5, 768), (768, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>422.845</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.047416666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.03921446323414612</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>385.496</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.424933333333333</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.03575073305563597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((300, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>287.137</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.392808333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02662896174641538</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>187.747</v>
+      </c>
+      <c r="G10" t="n">
+        <v>125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.501976</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01741157594111608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((12, 5, 64), (12, 64, 5))</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((320, 64, 1), (320, 1, 64))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>185.697</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.09495</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01722145982379177</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>((5308416, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>176.768</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.838400000000002</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0163933882083826</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (12, 5, 64))</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (320, 64, 1))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>167.428</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.790466666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01552720062993914</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>((1, 5, 12, 64), (1, 5, 12, 64), ())</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>((3840, 768, 64, 1), (3840, 64, 320, 1), ())</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>163.172</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.719533333333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01513250102245998</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.339166666666666</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01301599856900852</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>115.748</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.929133333333333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0107344196819779</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072),)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1),)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>105.021</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.75035</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.009739602320739891</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>94.07900000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.567983333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.008724845952075188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), (1, 5, 3072))</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), (15360, 3072, 1))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>89.14700000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.485783333333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.008267454395663716</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>86.495</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.441583333333333</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.008021509057544653</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>83.104</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.540266666666667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.007707029177619409</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>((1, 3, 1008, 1008), (1024, 3, 14, 14), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>((3048192, 1016064, 1008, 1), (588, 196, 14, 1), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('', '', '[0, 0]', '[14, 14]', '[1, 1]', '1', 'False', 'False', 'True')</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.004483958181771015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>35.168</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.344533333333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.003261465177590963</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>((1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('', '2', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>31.743</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.1743</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.002943832152305219</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>((49408, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.632</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.002611546275050088</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>((1, 768), (1, 1))</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>26.687</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.6687</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.002474940889284862</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>((16, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>26.463</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.2926</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.002454167225733327</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>24.704</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.9408</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.002291038323112123</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 768, 1))</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (768, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>23.615</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.00219004493200667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>22.176</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.4352</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.002056592691601945</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4), (5184, 4), ())</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1), (4, 1), ())</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>22.144</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.428800000000001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.002053625025380297</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>((1, 1024), (), (1024,), (1024,), ())</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>((5309440, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('', '[1024]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>20.128</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.0256</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.001866662053416484</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 768))</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>18.784</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7568</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.001742020072107275</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>((1, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>((5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>18.527</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.7054</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.001718186002764666</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>((1, 1024), (1024, 768))</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>((1024, 1), (1, 1024))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>17.918</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.5836</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.00166170760498393</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>15.936</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.1872</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.001477897778380618</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>15.296</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.5296</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.001418544453947662</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('', '', '')</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>14.657</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.9314</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.001359283869084131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.912</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.001350288130849762</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>13.985</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.001296962878429527</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 1))</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>13.183</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.6366</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.001222585743749479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>12.223</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.4446</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.001133555757100044</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>((5,), (5, 1))</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>((1,), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>10.687</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.1374</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.000991107778460948</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 1))</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10.143</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.000940657452692935</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.0096</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0009318471935974179</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9.247</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.8494</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0008575627984867958</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4),)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1),)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>8.896000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.7792</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.0008250112096180963</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8.798999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.7598</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0008160154713837261</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8.769</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.7538</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.0008132332843009313</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>((1, 5), (1, 5), ())</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0008012698798449135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>('', '1.', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>8.478999999999999</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.0007863388091672478</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8.446999999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.6894</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0007833711429456</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7.872</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.5744</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0007300458905253656</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>((5,), (), ())</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>((1,), (), ())</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.5488</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.0007181752256387743</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>('', '', '0')</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>7.454000000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.0006912807505050909</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>7.425</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.0006885913029917225</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>('', '', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>7.134</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0006616040882886126</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>('0', '5', '1', '')</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>7.104</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.4208</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0006588219012058177</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>((), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>((), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0006528865687625221</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>7.009</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.4018</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.0006500116421103007</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>((5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>7.008</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.4016</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0006499189025408743</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>('0', '1', '1', '')</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.2352</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.0005727595807780308</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5.984</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.1968</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.0005549535834481437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20397,7 +27117,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20441,28 +27161,46 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="K46" t="n">
         <v>10</v>
       </c>
       <c r="L46" t="n">
-        <v>173.092</v>
+        <v>207.634</v>
       </c>
       <c r="M46" t="n">
-        <v>17.3092</v>
+        <v>20.7634</v>
       </c>
       <c r="N46" t="n">
-        <v>7.994499745311009</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+        <v>10.99204100146</v>
+      </c>
+      <c r="O46" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0.0004869541317567053</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.644985869825148e-05</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.0002431604507081597</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.820122983111647e-05</v>
+      </c>
       <c r="W46" t="n">
         <v>3.174267578125</v>
       </c>
@@ -20473,20 +27211,32 @@
         <v>31.74267578125</v>
       </c>
       <c r="Z46" t="n">
-        <v>17.22</v>
+        <v>19.61</v>
       </c>
       <c r="AA46" t="n">
-        <v>9.619999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="AB46" t="n">
-        <v>25.261</v>
-      </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
+        <v>38.951</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.0004785382020962185</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.0004331143348229632</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.0005400469781397342</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.0002389579578737944</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.0002162755586112066</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.0002696723531933133</v>
+      </c>
       <c r="AI46" t="n">
         <v>3.2159423828125</v>
       </c>
@@ -20506,9 +27256,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP46" t="n">
         <v>0.005600731403536479</v>
@@ -20923,7 +27677,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -20953,7 +27707,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -20963,32 +27717,50 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4578</v>
+        <v>4577</v>
       </c>
       <c r="K50" t="n">
         <v>5</v>
       </c>
       <c r="L50" t="n">
-        <v>85.33199999999999</v>
+        <v>93.05199999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>17.0664</v>
+        <v>18.6104</v>
       </c>
       <c r="N50" t="n">
-        <v>1.155311343318327</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+        <v>1.133556482933252</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="P50" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>1.61185101736415</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.02189358768515036</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.8059253062550091</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.01094679109303155</v>
+      </c>
       <c r="W50" t="n">
         <v>4.940771484375</v>
       </c>
@@ -20999,20 +27771,32 @@
         <v>24.703857421875</v>
       </c>
       <c r="Z50" t="n">
-        <v>16.78</v>
+        <v>18.39</v>
       </c>
       <c r="AA50" t="n">
-        <v>16</v>
+        <v>17.51</v>
       </c>
       <c r="AB50" t="n">
-        <v>18.941</v>
-      </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
+        <v>20.431</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.605380788344162</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.595095422115714</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.647883796281326</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.80269019255759</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.7975475107350711</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.8239416911883589</v>
+      </c>
       <c r="AI50" t="n">
         <v>4.9599609375</v>
       </c>
@@ -21032,9 +27816,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 3981312, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP50" t="n">
         <v>0.004358790386943698</v>
@@ -22530,7 +29318,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -22560,7 +29348,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -22570,32 +29358,50 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>4582</v>
+        <v>4581</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>51.332</v>
+        <v>56.662</v>
       </c>
       <c r="M61" t="n">
-        <v>10.2664</v>
+        <v>11.3324</v>
       </c>
       <c r="N61" t="n">
-        <v>0.2338146701984292</v>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+        <v>0.3035264403639328</v>
+      </c>
+      <c r="O61" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>0.0004849575764314781</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.789683268713756e-05</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.0002421634711959526</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.892377601022212e-05</v>
+      </c>
       <c r="W61" t="n">
         <v>3.187255859375</v>
       </c>
@@ -22606,20 +29412,32 @@
         <v>15.936279296875</v>
       </c>
       <c r="Z61" t="n">
-        <v>10.21</v>
+        <v>11.211</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.091</v>
+        <v>11.071</v>
       </c>
       <c r="AB61" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
+        <v>11.85</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.0004954890671700488</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.000440935675789179</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.0005224021892362551</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0.000247422369042001</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.0002201811436970673</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0.0002608614312961274</v>
+      </c>
       <c r="AI61" t="n">
         <v>3.10400390625</v>
       </c>
@@ -22639,9 +29457,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP61" t="n">
         <v>0.002811824073327106</v>

--- a/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'elementwise', 'other'}</t>
+          <t>{'other', 'elementwise'}</t>
         </is>
       </c>
       <c r="H5" t="n">

--- a/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/h100/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,13 +30,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,12 +58,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,17 +442,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>time ms</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
@@ -565,202 +577,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: op_shape</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: num_channels</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: has_bias</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: is_affine</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: is_training</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -787,7 +799,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1024</t>
@@ -869,12 +885,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': np.float64(3701.084), 'mean_duration_us': np.float64(14.804336), 'median_duration_us': np.float64(14.56), 'std_dev_duration_us': np.float64(0.5479889406767253), 'min_duration_us': np.float64(13.952), 'max_duration_us': np.float64(15.807)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': 3701.084, 'mean_duration_us': 14.804336, 'median_duration_us': 14.56, 'std_dev_duration_us': 0.5479889406767253, 'min_duration_us': 13.952, 'max_duration_us': 15.807}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.8)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.8}]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -943,7 +959,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1025,12 +1045,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': np.float64(3701.084), 'mean_duration_us': np.float64(14.804336), 'median_duration_us': np.float64(14.56), 'std_dev_duration_us': np.float64(0.5479889406767253), 'min_duration_us': np.float64(13.952), 'max_duration_us': np.float64(15.807)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': 3701.084, 'mean_duration_us': 14.804336, 'median_duration_us': 14.56, 'std_dev_duration_us': 0.5479889406767253, 'min_duration_us': 13.952, 'max_duration_us': 15.807}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.8)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.8}]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1099,7 +1119,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>768</t>
@@ -1181,12 +1205,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(451.14099999999996), 'mean_duration_us': np.float64(3.6091279999999997), 'median_duration_us': np.float64(3.584), 'std_dev_duration_us': np.float64(0.16081094370719926), 'min_duration_us': np.float64(3.328), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': 451.14099999999996, 'mean_duration_us': 3.6091279999999997, 'median_duration_us': 3.584, 'std_dev_duration_us': 0.16081094370719926, 'min_duration_us': 3.328, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(3.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 3.61}]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1255,7 +1279,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>768</t>
@@ -1337,12 +1365,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(451.14099999999996), 'mean_duration_us': np.float64(3.6091279999999997), 'median_duration_us': np.float64(3.584), 'std_dev_duration_us': np.float64(0.16081094370719926), 'min_duration_us': np.float64(3.328), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': 451.14099999999996, 'mean_duration_us': 3.6091279999999997, 'median_duration_us': 3.584, 'std_dev_duration_us': 0.16081094370719926, 'min_duration_us': 3.328, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(3.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 3.61}]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1411,7 +1439,11 @@
           <t>(5308416, 1024, 1)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1493,12 +1525,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(70.463), 'mean_duration_us': np.float64(14.0926), 'median_duration_us': np.float64(14.079), 'std_dev_duration_us': np.float64(0.1321144957981524), 'min_duration_us': np.float64(13.92), 'max_duration_us': np.float64(14.272)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 70.463, 'mean_duration_us': 14.0926, 'median_duration_us': 14.079, 'std_dev_duration_us': 0.1321144957981524, 'min_duration_us': 13.92, 'max_duration_us': 14.272}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.09)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.09}]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1567,7 +1599,11 @@
           <t>(5308416, 1024, 1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1649,12 +1685,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(70.463), 'mean_duration_us': np.float64(14.0926), 'median_duration_us': np.float64(14.079), 'std_dev_duration_us': np.float64(0.1321144957981524), 'min_duration_us': np.float64(13.92), 'max_duration_us': np.float64(14.272)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 70.463, 'mean_duration_us': 14.0926, 'median_duration_us': 14.079, 'std_dev_duration_us': 0.1321144957981524, 'min_duration_us': 13.92, 'max_duration_us': 14.272}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.09)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.09}]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1723,7 +1759,11 @@
           <t>(5309440, 1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1805,12 +1845,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.128), 'mean_duration_us': np.float64(4.0256), 'median_duration_us': np.float64(4.0), 'std_dev_duration_us': np.float64(0.13636656481704024), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(4.224)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 20.128, 'mean_duration_us': 4.0256, 'median_duration_us': 4.0, 'std_dev_duration_us': 0.13636656481704024, 'min_duration_us': 3.808, 'max_duration_us': 4.224}]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.03)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 4.03}]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1879,7 +1919,11 @@
           <t>(5309440, 1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1961,12 +2005,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.128), 'mean_duration_us': np.float64(4.0256), 'median_duration_us': np.float64(4.0), 'std_dev_duration_us': np.float64(0.13636656481704024), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(4.224)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 20.128, 'mean_duration_us': 4.0256, 'median_duration_us': 4.0, 'std_dev_duration_us': 0.13636656481704024, 'min_duration_us': 3.808, 'max_duration_us': 4.224}]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.03)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 4.03}]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2029,182 +2073,182 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: num_input_elems</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: num_output_elems</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: reduce_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -2297,12 +2341,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(47.679), 'mean_duration_us': np.float64(3.1786000000000003), 'median_duration_us': np.float64(3.136), 'std_dev_duration_us': np.float64(0.22485248497626176), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 15, 'total_duration_us': 47.679, 'mean_duration_us': 3.1786000000000003, 'median_duration_us': 3.136, 'std_dev_duration_us': 0.22485248497626176, 'min_duration_us': 2.848, 'max_duration_us': 3.551}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.18)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 3.18}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -2437,12 +2481,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(24.704), 'mean_duration_us': np.float64(4.9408), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.05935115837117255), 'min_duration_us': np.float64(4.832), 'max_duration_us': np.float64(4.992)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 24.704, 'mean_duration_us': 4.9408, 'median_duration_us': 4.96, 'std_dev_duration_us': 0.05935115837117255, 'min_duration_us': 4.832, 'max_duration_us': 4.992}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 4.94}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -2729,57 +2773,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parent op category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Parent cpu_op</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kernel name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Kernel stream</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_sum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_count</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_max</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Percent of kernels time (%)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Percent of total time (%)</t>
         </is>
@@ -5096,17 +5140,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>bin_start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>bin_end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -6227,47 +6271,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parent cpu_op</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Input dims</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Input strides</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kernel name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) sum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel count</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) percent of total time</t>
         </is>
@@ -8577,27 +8621,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aten::fill_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>((5, 5), ())</t>
+          <t>((1, 1), ())</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>((5, 1), ())</t>
+          <t>((1, 1), ())</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>('', '-3.3895313892515355e+38')</t>
+          <t>('', '')</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -8616,27 +8660,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::fill_</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>((1, 1), ())</t>
+          <t>((5, 5), ())</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>((1, 1), ())</t>
+          <t>((5, 1), ())</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>('', '')</t>
+          <t>('', '-3.3895313892515355e+38')</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -8745,27 +8789,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -8900,37 +8944,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -9707,107 +9751,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>process_label</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>thread_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -9885,12 +9929,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(262422.467), 'mean_duration_us': np.float64(2186.8538916666666), 'median_duration_us': np.float64(2170.955), 'std_dev_duration_us': np.float64(52.45910857528236), 'min_duration_us': np.float64(2146.764), 'max_duration_us': np.float64(2395.817)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'count': 120, 'total_duration_us': 262422.467, 'mean_duration_us': 2186.8538916666666, 'median_duration_us': 2170.955, 'std_dev_duration_us': 52.45910857528236, 'min_duration_us': 2146.764, 'max_duration_us': 2395.817}]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c...', 'stream': 7, 'mean_duration_us': np.float64(2186.85)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c...', 'stream': 7, 'mean_duration_us': 2186.85}]</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -9972,12 +10016,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(130015.7), 'mean_duration_us': np.float64(1083.4641666666666), 'median_duration_us': np.float64(1082.965), 'std_dev_duration_us': np.float64(3.932529614919927), 'min_duration_us': np.float64(1075.574), 'max_duration_us': np.float64(1096.694)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 130015.7, 'mean_duration_us': 1083.4641666666666, 'median_duration_us': 1082.965, 'std_dev_duration_us': 3.932529614919927, 'min_duration_us': 1075.574, 'max_duration_us': 1096.694}]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': np.float64(1083.46)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': 1083.46}]</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -10059,12 +10103,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(99311.41), 'mean_duration_us': np.float64(827.5950833333334), 'median_duration_us': np.float64(826.9205), 'std_dev_duration_us': np.float64(2.9474507419783706), 'min_duration_us': np.float64(825.432), 'max_duration_us': np.float64(851.8)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 99311.41, 'mean_duration_us': 827.5950833333334, 'median_duration_us': 826.9205, 'std_dev_duration_us': 2.9474507419783706, 'min_duration_us': 825.432, 'max_duration_us': 851.8}]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': np.float64(827.6)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': 827.6}]</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -10146,12 +10190,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(449.6640000000001), 'mean_duration_us': np.float64(0.9368000000000002), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.14700191892171566), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.408)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(10035.521), 'mean_duration_us': np.float64(20.90733541666667), 'median_duration_us': np.float64(20.912), 'std_dev_duration_us': np.float64(0.2994497001373127), 'min_duration_us': np.float64(20.256), 'max_duration_us': np.float64(22.015)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': 449.6640000000001, 'mean_duration_us': 0.9368000000000002, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.14700191892171566, 'min_duration_us': 0.767, 'max_duration_us': 1.408}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': 10035.521, 'mean_duration_us': 20.90733541666667, 'median_duration_us': 20.912, 'std_dev_duration_us': 0.2994497001373127, 'min_duration_us': 20.256, 'max_duration_us': 22.015}]</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.94)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.91)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.94}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.91}]</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -10233,12 +10277,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8133.554), 'mean_duration_us': np.float64(1626.7108), 'median_duration_us': np.float64(347.196), 'std_dev_duration_us': np.float64(1579.6924965375256), 'min_duration_us': np.float64(325.565), 'max_duration_us': np.float64(3620.445)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 8133.554, 'mean_duration_us': 1626.7108, 'median_duration_us': 347.196, 'std_dev_duration_us': 1579.6924965375256, 'min_duration_us': 325.565, 'max_duration_us': 3620.445}]</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(1626.71)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 1626.71}]</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -10320,12 +10364,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(115.61200000000002), 'mean_duration_us': np.float64(0.9634333333333335), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.18370559478566667), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.6)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(7766.737), 'mean_duration_us': np.float64(64.72280833333333), 'median_duration_us': np.float64(64.639), 'std_dev_duration_us': np.float64(0.5570301951096441), 'min_duration_us': np.float64(63.711), 'max_duration_us': np.float64(65.951)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 115.61200000000002, 'mean_duration_us': 0.9634333333333335, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.18370559478566667, 'min_duration_us': 0.768, 'max_duration_us': 1.6}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 7766.737, 'mean_duration_us': 64.72280833333333, 'median_duration_us': 64.639, 'std_dev_duration_us': 0.5570301951096441, 'min_duration_us': 63.711, 'max_duration_us': 65.951}]</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.96)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(64.72)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.96}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 64.72}]</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -10407,12 +10451,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(116.09), 'mean_duration_us': np.float64(0.9674166666666667), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.15527371441711854), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.568)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(6884.5689999999995), 'mean_duration_us': np.float64(57.37140833333333), 'median_duration_us': np.float64(57.344), 'std_dev_duration_us': np.float64(0.31250691981227396), 'min_duration_us': np.float64(56.639), 'max_duration_us': np.float64(58.048)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 116.09, 'mean_duration_us': 0.9674166666666667, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.15527371441711854, 'min_duration_us': 0.768, 'max_duration_us': 1.568}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 6884.5689999999995, 'mean_duration_us': 57.37140833333333, 'median_duration_us': 57.344, 'std_dev_duration_us': 0.31250691981227396, 'min_duration_us': 56.639, 'max_duration_us': 58.048}]</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.97)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(57.37)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.97}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 57.37}]</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -10494,12 +10538,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(5223.73), 'mean_duration_us': np.float64(43.53108333333333), 'median_duration_us': np.float64(43.3595), 'std_dev_duration_us': np.float64(0.6410638629566389), 'min_duration_us': np.float64(42.656), 'max_duration_us': np.float64(44.704)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 5223.73, 'mean_duration_us': 43.53108333333333, 'median_duration_us': 43.3595, 'std_dev_duration_us': 0.6410638629566389, 'min_duration_us': 42.656, 'max_duration_us': 44.704}]</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(43.53)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 43.53}]</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -10581,12 +10625,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': np.float64(5038.033), 'mean_duration_us': np.float64(13.994536111111112), 'median_duration_us': np.float64(13.152), 'std_dev_duration_us': np.float64(1.3500063184322875), 'min_duration_us': np.float64(12.736), 'max_duration_us': np.float64(16.288)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': 5038.033, 'mean_duration_us': 13.994536111111112, 'median_duration_us': 13.152, 'std_dev_duration_us': 1.3500063184322875, 'min_duration_us': 12.736, 'max_duration_us': 16.288}]</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.99}]</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -10668,12 +10712,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3988.498), 'mean_duration_us': np.float64(33.23748333333334), 'median_duration_us': np.float64(33.055), 'std_dev_duration_us': np.float64(0.39268874407375365), 'min_duration_us': np.float64(32.8), 'max_duration_us': np.float64(34.272)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3988.498, 'mean_duration_us': 33.23748333333334, 'median_duration_us': 33.055, 'std_dev_duration_us': 0.39268874407375365, 'min_duration_us': 32.8, 'max_duration_us': 34.272}]</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(33.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 33.24}]</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -10755,12 +10799,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': np.float64(3701.084), 'mean_duration_us': np.float64(14.804336), 'median_duration_us': np.float64(14.56), 'std_dev_duration_us': np.float64(0.5479889406767253), 'min_duration_us': np.float64(13.952), 'max_duration_us': np.float64(15.807)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': 3701.084, 'mean_duration_us': 14.804336, 'median_duration_us': 14.56, 'std_dev_duration_us': 0.5479889406767253, 'min_duration_us': 13.952, 'max_duration_us': 15.807}]</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.8)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.8}]</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -10842,12 +10886,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3687.3240000000005), 'mean_duration_us': np.float64(30.727700000000006), 'median_duration_us': np.float64(30.591), 'std_dev_duration_us': np.float64(0.3214868737600341), 'min_duration_us': np.float64(30.336), 'max_duration_us': np.float64(31.711)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3687.3240000000005, 'mean_duration_us': 30.727700000000006, 'median_duration_us': 30.591, 'std_dev_duration_us': 0.3214868737600341, 'min_duration_us': 30.336, 'max_duration_us': 31.711}]</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(30.73)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 30.73}]</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -10929,12 +10973,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2338.761), 'mean_duration_us': np.float64(467.7522), 'median_duration_us': np.float64(464.252), 'std_dev_duration_us': np.float64(11.281809454161158), 'min_duration_us': np.float64(454.556), 'max_duration_us': np.float64(487.899)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2338.761, 'mean_duration_us': 467.7522, 'median_duration_us': 464.252, 'std_dev_duration_us': 11.281809454161158, 'min_duration_us': 454.556, 'max_duration_us': 487.899}]</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(467.75)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 467.75}]</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -11016,12 +11060,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2324.394), 'mean_duration_us': np.float64(464.87879999999996), 'median_duration_us': np.float64(472.188), 'std_dev_duration_us': np.float64(19.601893596282974), 'min_duration_us': np.float64(436.444), 'max_duration_us': np.float64(489.34)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2324.394, 'mean_duration_us': 464.87879999999996, 'median_duration_us': 472.188, 'std_dev_duration_us': 19.601893596282974, 'min_duration_us': 436.444, 'max_duration_us': 489.34}]</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(464.88)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 464.88}]</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -11103,12 +11147,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': np.float64(2317.353), 'mean_duration_us': np.float64(9.458583673469388), 'median_duration_us': np.float64(9.472), 'std_dev_duration_us': np.float64(0.3348456698101192), 'min_duration_us': np.float64(8.576), 'max_duration_us': np.float64(10.849)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': 2317.353, 'mean_duration_us': 9.458583673469388, 'median_duration_us': 9.472, 'std_dev_duration_us': 0.3348456698101192, 'min_duration_us': 8.576, 'max_duration_us': 10.849}]</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(9.46)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 9.46}]</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -11190,12 +11234,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(1873.8329999999999), 'mean_duration_us': np.float64(15.615274999999999), 'median_duration_us': np.float64(15.584), 'std_dev_duration_us': np.float64(0.1854254999768552), 'min_duration_us': np.float64(15.264), 'max_duration_us': np.float64(16.384)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 1873.8329999999999, 'mean_duration_us': 15.615274999999999, 'median_duration_us': 15.584, 'std_dev_duration_us': 0.1854254999768552, 'min_duration_us': 15.264, 'max_duration_us': 16.384}]</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(15.62)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 15.62}]</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -11277,12 +11321,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(1627.952), 'mean_duration_us': np.float64(325.5904), 'median_duration_us': np.float64(333.501), 'std_dev_duration_us': np.float64(11.368233417730304), 'min_duration_us': np.float64(304.989), 'max_duration_us': np.float64(334.205)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 1627.952, 'mean_duration_us': 325.5904, 'median_duration_us': 333.501, 'std_dev_duration_us': 11.368233417730304, 'min_duration_us': 304.989, 'max_duration_us': 334.205}]</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(325.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 325.59}]</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -11364,12 +11408,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': np.float64(1579.851), 'mean_duration_us': np.float64(6.5827125), 'median_duration_us': np.float64(6.592), 'std_dev_duration_us': np.float64(0.13116311667951205), 'min_duration_us': np.float64(6.303), 'max_duration_us': np.float64(6.975)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': 1579.851, 'mean_duration_us': 6.5827125, 'median_duration_us': 6.592, 'std_dev_duration_us': 0.13116311667951205, 'min_duration_us': 6.303, 'max_duration_us': 6.975}]</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.58)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.58}]</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -11451,12 +11495,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(28.127000000000002), 'mean_duration_us': np.float64(5.625400000000001), 'median_duration_us': np.float64(5.664), 'std_dev_duration_us': np.float64(0.08941498755801505), 'min_duration_us': np.float64(5.503), 'max_duration_us': np.float64(5.728)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(222.207), 'mean_duration_us': np.float64(44.4414), 'median_duration_us': np.float64(44.384), 'std_dev_duration_us': np.float64(0.1792647204555328), 'min_duration_us': np.float64(44.224), 'max_duration_us': np.float64(44.768)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.85), 'mean_duration_us': np.float64(2.17), 'median_duration_us': np.float64(2.176), 'std_dev_duration_us': np.float64(0.013007690033207267), 'min_duration_us': np.float64(2.144), 'max_duration_us': np.float64(2.177)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(58.303000000000004), 'mean_duration_us': np.float64(11.6606), 'median_duration_us': np.float64(11.679), 'std_dev_duration_us': np.float64(0.15088485676170435), 'min_duration_us': np.float64(11.424), 'max_duration_us': np.float64(11.872)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(982.9660000000001), 'mean_duration_us': np.float64(196.59320000000002), 'median_duration_us': np.float64(196.542), 'std_dev_duration_us': np.float64(0.4292092263686784), 'min_duration_us': np.float64(195.966), 'max_duration_us': np.float64(197.245)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(48.35), 'mean_duration_us': np.float64(9.67), 'median_duration_us': np.float64(9.663), 'std_dev_duration_us': np.float64(0.0547539952880155), 'min_duration_us': np.float64(9.6), 'max_duration_us': np.float64(9.759)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 28.127000000000002, 'mean_duration_us': 5.625400000000001, 'median_duration_us': 5.664, 'std_dev_duration_us': 0.08941498755801505, 'min_duration_us': 5.503, 'max_duration_us': 5.728}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 222.207, 'mean_duration_us': 44.4414, 'median_duration_us': 44.384, 'std_dev_duration_us': 0.1792647204555328, 'min_duration_us': 44.224, 'max_duration_us': 44.768}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 10.85, 'mean_duration_us': 2.17, 'median_duration_us': 2.176, 'std_dev_duration_us': 0.013007690033207267, 'min_duration_us': 2.144, 'max_duration_us': 2.177}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 58.303000000000004, 'mean_duration_us': 11.6606, 'median_duration_us': 11.679, 'std_dev_duration_us': 0.15088485676170435, 'min_duration_us': 11.424, 'max_duration_us': 11.872}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 982.9660000000001, 'mean_duration_us': 196.59320000000002, 'median_duration_us': 196.542, 'std_dev_duration_us': 0.4292092263686784, 'min_duration_us': 195.966, 'max_duration_us': 197.245}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 48.35, 'mean_duration_us': 9.67, 'median_duration_us': 9.663, 'std_dev_duration_us': 0.0547539952880155, 'min_duration_us': 9.6, 'max_duration_us': 9.759}]</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(5.63)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(44.44)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.17)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(11.66)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(196.59)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(9.67)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 5.63}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 44.44}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 2.17}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 11.66}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': 196.59}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 9.67}]</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -11538,12 +11582,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(934.809), 'mean_duration_us': np.float64(7.790075), 'median_duration_us': np.float64(7.776), 'std_dev_duration_us': np.float64(0.06863528763204346), 'min_duration_us': np.float64(7.711), 'max_duration_us': np.float64(8.032)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 934.809, 'mean_duration_us': 7.790075, 'median_duration_us': 7.776, 'std_dev_duration_us': 0.06863528763204346, 'min_duration_us': 7.711, 'max_duration_us': 8.032}]</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(7.79)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 7.79}]</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -11625,12 +11669,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(385.4959999999999), 'mean_duration_us': np.float64(6.424933333333332), 'median_duration_us': np.float64(6.336), 'std_dev_duration_us': np.float64(0.19279919317489072), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(6.912)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(140.35000000000002), 'mean_duration_us': np.float64(2.339166666666667), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.037292164801142315), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.496)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 385.4959999999999, 'mean_duration_us': 6.424933333333332, 'median_duration_us': 6.336, 'std_dev_duration_us': 0.19279919317489072, 'min_duration_us': 6.239, 'max_duration_us': 6.912}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': 140.35000000000002, 'mean_duration_us': 2.339166666666667, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.037292164801142315, 'min_duration_us': 2.272, 'max_duration_us': 2.496}]</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.42)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.42}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 2.34}]</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -11712,12 +11756,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': np.float64(457.9199999999999), 'mean_duration_us': np.float64(2.5439999999999996), 'median_duration_us': np.float64(2.4645), 'std_dev_duration_us': np.float64(0.22104903930525865), 'min_duration_us': np.float64(2.24), 'max_duration_us': np.float64(3.232)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': 457.9199999999999, 'mean_duration_us': 2.5439999999999996, 'median_duration_us': 2.4645, 'std_dev_duration_us': 0.22104903930525865, 'min_duration_us': 2.24, 'max_duration_us': 3.232}]</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.54}]</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -11799,12 +11843,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(451.14099999999996), 'mean_duration_us': np.float64(3.6091279999999997), 'median_duration_us': np.float64(3.584), 'std_dev_duration_us': np.float64(0.16081094370719926), 'min_duration_us': np.float64(3.328), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': 451.14099999999996, 'mean_duration_us': 3.6091279999999997, 'median_duration_us': 3.584, 'std_dev_duration_us': 0.16081094370719926, 'min_duration_us': 3.328, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(3.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 3.61}]</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -11886,12 +11930,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(17.248), 'mean_duration_us': np.float64(0.8624), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.13365305832639968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.248)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(414.7149999999999), 'mean_duration_us': np.float64(20.735749999999996), 'median_duration_us': np.float64(20.768), 'std_dev_duration_us': np.float64(0.42032010123238245), 'min_duration_us': np.float64(19.936), 'max_duration_us': np.float64(21.279)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': 17.248, 'mean_duration_us': 0.8624, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.13365305832639968, 'min_duration_us': 0.768, 'max_duration_us': 1.248}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': 414.7149999999999, 'mean_duration_us': 20.735749999999996, 'median_duration_us': 20.768, 'std_dev_duration_us': 0.42032010123238245, 'min_duration_us': 19.936, 'max_duration_us': 21.279}]</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.86)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.74)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.86}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.74}]</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -11973,12 +12017,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(422.845), 'mean_duration_us': np.float64(7.047416666666667), 'median_duration_us': np.float64(6.976), 'std_dev_duration_us': np.float64(0.17790056133194818), 'min_duration_us': np.float64(6.752), 'max_duration_us': np.float64(7.52)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 422.845, 'mean_duration_us': 7.047416666666667, 'median_duration_us': 6.976, 'std_dev_duration_us': 0.17790056133194818, 'min_duration_us': 6.752, 'max_duration_us': 7.52}]</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(7.05)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 7.05}]</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -12060,12 +12104,12 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(287.13699999999994), 'mean_duration_us': np.float64(2.392808333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.24387456802740948), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.913)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 287.13699999999994, 'mean_duration_us': 2.392808333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.24387456802740948, 'min_duration_us': 1.984, 'max_duration_us': 2.913}]</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.39)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.39}]</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -12147,12 +12191,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(219.806), 'mean_duration_us': np.float64(43.961200000000005), 'median_duration_us': np.float64(43.712), 'std_dev_duration_us': np.float64(0.48020553932665044), 'min_duration_us': np.float64(43.551), 'max_duration_us': np.float64(44.799)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 5, 'total_duration_us': 219.806, 'mean_duration_us': 43.961200000000005, 'median_duration_us': 43.712, 'std_dev_duration_us': 0.48020553932665044, 'min_duration_us': 43.551, 'max_duration_us': 44.799}]</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(43.96)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': 43.96}]</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -12234,12 +12278,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(195.071), 'mean_duration_us': np.float64(39.0142), 'median_duration_us': np.float64(39.072), 'std_dev_duration_us': np.float64(0.2134070289376613), 'min_duration_us': np.float64(38.624), 'max_duration_us': np.float64(39.231)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 195.071, 'mean_duration_us': 39.0142, 'median_duration_us': 39.072, 'std_dev_duration_us': 0.2134070289376613, 'min_duration_us': 38.624, 'max_duration_us': 39.231}]</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(39.01)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 39.01}]</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -12321,12 +12365,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(187.747), 'mean_duration_us': np.float64(1.5019760000000002), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.09206636423797784), 'min_duration_us': np.float64(1.344), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': 187.747, 'mean_duration_us': 1.5019760000000002, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.09206636423797784, 'min_duration_us': 1.344, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.5}]</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -12408,12 +12452,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(185.69699999999997), 'mean_duration_us': np.float64(3.0949499999999994), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.04453478977159322), 'min_duration_us': np.float64(3.008), 'max_duration_us': np.float64(3.168)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 185.69699999999997, 'mean_duration_us': 3.0949499999999994, 'median_duration_us': 3.104, 'std_dev_duration_us': 0.04453478977159322, 'min_duration_us': 3.008, 'max_duration_us': 3.168}]</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(3.09)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 3.09}]</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -12495,12 +12539,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(176.76800000000006), 'mean_duration_us': np.float64(8.838400000000004), 'median_duration_us': np.float64(8.832), 'std_dev_duration_us': np.float64(0.06681796165702758), 'min_duration_us': np.float64(8.704), 'max_duration_us': np.float64(8.992)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 20, 'total_duration_us': 176.76800000000006, 'mean_duration_us': 8.838400000000004, 'median_duration_us': 8.832, 'std_dev_duration_us': 0.06681796165702758, 'min_duration_us': 8.704, 'max_duration_us': 8.992}]</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(8.84)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': 8.84}]</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -12582,12 +12626,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(167.428), 'mean_duration_us': np.float64(2.7904666666666667), 'median_duration_us': np.float64(2.816), 'std_dev_duration_us': np.float64(0.037250264726874344), 'min_duration_us': np.float64(2.72), 'max_duration_us': np.float64(2.88)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 167.428, 'mean_duration_us': 2.7904666666666667, 'median_duration_us': 2.816, 'std_dev_duration_us': 0.037250264726874344, 'min_duration_us': 2.72, 'max_duration_us': 2.88}]</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(2.79)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 2.79}]</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -12669,12 +12713,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(163.17200000000005), 'mean_duration_us': np.float64(2.719533333333334), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.14011381881250043), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': 163.17200000000005, 'mean_duration_us': 2.719533333333334, 'median_duration_us': 2.784, 'std_dev_duration_us': 0.14011381881250043, 'min_duration_us': 2.527, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -12756,12 +12800,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(35.168), 'mean_duration_us': np.float64(2.344533333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.10418372660300108), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.56)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(83.104), 'mean_duration_us': np.float64(5.540266666666667), 'median_duration_us': np.float64(5.376), 'std_dev_duration_us': np.float64(0.32818683025916123), 'min_duration_us': np.float64(5.152), 'max_duration_us': np.float64(6.176)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': 35.168, 'mean_duration_us': 2.344533333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.10418372660300108, 'min_duration_us': 2.176, 'max_duration_us': 2.56}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': 83.104, 'mean_duration_us': 5.540266666666667, 'median_duration_us': 5.376, 'std_dev_duration_us': 0.32818683025916123, 'min_duration_us': 5.152, 'max_duration_us': 6.176}]</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(5.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.34}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 5.54}]</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -12843,12 +12887,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(115.74799999999999), 'mean_duration_us': np.float64(1.9291333333333331), 'median_duration_us': np.float64(1.857), 'std_dev_duration_us': np.float64(0.09073284349610612), 'min_duration_us': np.float64(1.824), 'max_duration_us': np.float64(2.049)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'count': 60, 'total_duration_us': 115.74799999999999, 'mean_duration_us': 1.9291333333333331, 'median_duration_us': 1.857, 'std_dev_duration_us': 0.09073284349610612, 'min_duration_us': 1.824, 'max_duration_us': 2.049}]</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 7, 'mean_duration_us': np.float64(1.93)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 7, 'mean_duration_us': 1.93}]</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -12930,12 +12974,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(105.02100000000002), 'mean_duration_us': np.float64(1.7503500000000003), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.021235838418422137), 'min_duration_us': np.float64(1.696), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 105.02100000000002, 'mean_duration_us': 1.7503500000000003, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.021235838418422137, 'min_duration_us': 1.696, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -13017,12 +13061,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(94.07899999999998), 'mean_duration_us': np.float64(1.567983333333333), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02925092116308288), 'min_duration_us': np.float64(1.535), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 94.07899999999998, 'mean_duration_us': 1.567983333333333, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02925092116308288, 'min_duration_us': 1.535, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -13104,12 +13148,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(89.14699999999999), 'mean_duration_us': np.float64(1.4857833333333332), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.016880058912482752), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.535)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 89.14699999999999, 'mean_duration_us': 1.4857833333333332, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.016880058912482752, 'min_duration_us': 1.471, 'max_duration_us': 1.535}]</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.49}]</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -13191,12 +13235,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(86.78200000000001), 'mean_duration_us': np.float64(17.3564), 'median_duration_us': np.float64(17.376), 'std_dev_duration_us': np.float64(0.07209049868047837), 'min_duration_us': np.float64(17.215), 'max_duration_us': np.float64(17.408)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': 86.78200000000001, 'mean_duration_us': 17.3564, 'median_duration_us': 17.376, 'std_dev_duration_us': 0.07209049868047837, 'min_duration_us': 17.215, 'max_duration_us': 17.408}]</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(17.36)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': 17.36}]</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -13278,12 +13322,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(86.49500000000002), 'mean_duration_us': np.float64(1.4415833333333337), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.10003121040733015), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 86.49500000000002, 'mean_duration_us': 1.4415833333333337, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.10003121040733015, 'min_duration_us': 1.28, 'max_duration_us': 1.568}]</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.44)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.44}]</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -13365,12 +13409,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(70.463), 'mean_duration_us': np.float64(14.0926), 'median_duration_us': np.float64(14.079), 'std_dev_duration_us': np.float64(0.1321144957981524), 'min_duration_us': np.float64(13.92), 'max_duration_us': np.float64(14.272)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 70.463, 'mean_duration_us': 14.0926, 'median_duration_us': 14.079, 'std_dev_duration_us': 0.1321144957981524, 'min_duration_us': 13.92, 'max_duration_us': 14.272}]</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.09)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.09}]</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -13452,12 +13496,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(65.407), 'mean_duration_us': np.float64(13.081399999999999), 'median_duration_us': np.float64(13.088), 'std_dev_duration_us': np.float64(0.058854396607220374), 'min_duration_us': np.float64(13.023), 'max_duration_us': np.float64(13.184)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 65.407, 'mean_duration_us': 13.081399999999999, 'median_duration_us': 13.088, 'std_dev_duration_us': 0.058854396607220374, 'min_duration_us': 13.023, 'max_duration_us': 13.184}]</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.08)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.08}]</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -13539,12 +13583,12 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(57.631), 'mean_duration_us': np.float64(11.5262), 'median_duration_us': np.float64(11.552), 'std_dev_duration_us': np.float64(0.0889413289759043), 'min_duration_us': np.float64(11.392), 'max_duration_us': np.float64(11.616)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 57.631, 'mean_duration_us': 11.5262, 'median_duration_us': 11.552, 'std_dev_duration_us': 0.0889413289759043, 'min_duration_us': 11.392, 'max_duration_us': 11.616}]</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(11.53)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 11.53}]</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -13626,12 +13670,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(56.54299999999999), 'mean_duration_us': np.float64(11.308599999999998), 'median_duration_us': np.float64(11.296), 'std_dev_duration_us': np.float64(0.10403768547983014), 'min_duration_us': np.float64(11.168), 'max_duration_us': np.float64(11.487)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 56.54299999999999, 'mean_duration_us': 11.308599999999998, 'median_duration_us': 11.296, 'std_dev_duration_us': 0.10403768547983014, 'min_duration_us': 11.168, 'max_duration_us': 11.487}]</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(11.31)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 11.31}]</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -13713,12 +13757,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(31.743), 'mean_duration_us': np.float64(3.1742999999999997), 'median_duration_us': np.float64(3.216), 'std_dev_duration_us': np.float64(0.22374005005809758), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': 31.743, 'mean_duration_us': 3.1742999999999997, 'median_duration_us': 3.216, 'std_dev_duration_us': 0.22374005005809758, 'min_duration_us': 2.848, 'max_duration_us': 3.551}]</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 3.17}]</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -13800,12 +13844,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(28.159999999999997), 'mean_duration_us': np.float64(5.632), 'median_duration_us': np.float64(5.792), 'std_dev_duration_us': np.float64(0.2638787600395301), 'min_duration_us': np.float64(5.28), 'max_duration_us': np.float64(5.888)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 28.159999999999997, 'mean_duration_us': 5.632, 'median_duration_us': 5.792, 'std_dev_duration_us': 0.2638787600395301, 'min_duration_us': 5.28, 'max_duration_us': 5.888}]</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(5.63)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 5.63}]</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -13887,12 +13931,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(26.686999999999998), 'mean_duration_us': np.float64(2.6687), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.20862696374150683), 'min_duration_us': np.float64(2.335), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': 26.686999999999998, 'mean_duration_us': 2.6687, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.20862696374150683, 'min_duration_us': 2.335, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -13974,12 +14018,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(26.463), 'mean_duration_us': np.float64(5.2926), 'median_duration_us': np.float64(5.216), 'std_dev_duration_us': np.float64(0.19653355947522047), 'min_duration_us': np.float64(5.088), 'max_duration_us': np.float64(5.599)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 26.463, 'mean_duration_us': 5.2926, 'median_duration_us': 5.216, 'std_dev_duration_us': 0.19653355947522047, 'min_duration_us': 5.088, 'max_duration_us': 5.599}]</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(5.29)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 5.29}]</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -14061,12 +14105,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(24.704), 'mean_duration_us': np.float64(4.9408), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.05935115837117255), 'min_duration_us': np.float64(4.832), 'max_duration_us': np.float64(4.992)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 24.704, 'mean_duration_us': 4.9408, 'median_duration_us': 4.96, 'std_dev_duration_us': 0.05935115837117255, 'min_duration_us': 4.832, 'max_duration_us': 4.992}]</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 4.94}]</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -14148,12 +14192,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(23.615000000000002), 'mean_duration_us': np.float64(4.723000000000001), 'median_duration_us': np.float64(4.704), 'std_dev_duration_us': np.float64(0.06861486719363401), 'min_duration_us': np.float64(4.64), 'max_duration_us': np.float64(4.831)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': 23.615000000000002, 'mean_duration_us': 4.723000000000001, 'median_duration_us': 4.704, 'std_dev_duration_us': 0.06861486719363401, 'min_duration_us': 4.64, 'max_duration_us': 4.831}]</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(4.72)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 4.72}]</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -14235,12 +14279,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.143), 'mean_duration_us': np.float64(2.0286), 'median_duration_us': np.float64(2.047), 'std_dev_duration_us': np.float64(0.02545270123189289), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.048)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.183000000000002), 'mean_duration_us': np.float64(2.6366000000000005), 'median_duration_us': np.float64(2.688), 'std_dev_duration_us': np.float64(0.08984341934721768), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 10.143, 'mean_duration_us': 2.0286, 'median_duration_us': 2.047, 'std_dev_duration_us': 0.02545270123189289, 'min_duration_us': 1.984, 'max_duration_us': 2.048}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.183000000000002, 'mean_duration_us': 2.6366000000000005, 'median_duration_us': 2.688, 'std_dev_duration_us': 0.08984341934721768, 'min_duration_us': 2.527, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': np.float64(2.03)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': np.float64(2.64)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': 2.03}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': 2.64}]</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -14322,12 +14366,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(22.176000000000002), 'mean_duration_us': np.float64(4.4352), 'median_duration_us': np.float64(4.256), 'std_dev_duration_us': np.float64(0.26400560600108475), 'min_duration_us': np.float64(4.192), 'max_duration_us': np.float64(4.832)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 22.176000000000002, 'mean_duration_us': 4.4352, 'median_duration_us': 4.256, 'std_dev_duration_us': 0.26400560600108475, 'min_duration_us': 4.192, 'max_duration_us': 4.832}]</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 7, 'mean_duration_us': np.float64(4.44)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 7, 'mean_duration_us': 4.44}]</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -14409,12 +14453,12 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(22.144000000000002), 'mean_duration_us': np.float64(4.428800000000001), 'median_duration_us': np.float64(4.416), 'std_dev_duration_us': np.float64(0.09621309682158638), 'min_duration_us': np.float64(4.32), 'max_duration_us': np.float64(4.608)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 22.144000000000002, 'mean_duration_us': 4.428800000000001, 'median_duration_us': 4.416, 'std_dev_duration_us': 0.09621309682158638, 'min_duration_us': 4.32, 'max_duration_us': 4.608}]</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': np.float64(4.43)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': 4.43}]</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -14496,12 +14540,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.255), 'mean_duration_us': np.float64(4.051), 'median_duration_us': np.float64(4.032), 'std_dev_duration_us': np.float64(0.02550294100687212), 'min_duration_us': np.float64(4.032), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 20.255, 'mean_duration_us': 4.051, 'median_duration_us': 4.032, 'std_dev_duration_us': 0.02550294100687212, 'min_duration_us': 4.032, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(4.05)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 4.05}]</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -14583,12 +14627,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.128), 'mean_duration_us': np.float64(4.0256), 'median_duration_us': np.float64(4.0), 'std_dev_duration_us': np.float64(0.13636656481704024), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(4.224)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 20.128, 'mean_duration_us': 4.0256, 'median_duration_us': 4.0, 'std_dev_duration_us': 0.13636656481704024, 'min_duration_us': 3.808, 'max_duration_us': 4.224}]</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.03)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 4.03}]</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -14670,12 +14714,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(18.784), 'mean_duration_us': np.float64(3.7567999999999997), 'median_duration_us': np.float64(3.744), 'std_dev_duration_us': np.float64(0.03263372488699366), 'min_duration_us': np.float64(3.712), 'max_duration_us': np.float64(3.808)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 18.784, 'mean_duration_us': 3.7567999999999997, 'median_duration_us': 3.744, 'std_dev_duration_us': 0.03263372488699366, 'min_duration_us': 3.712, 'max_duration_us': 3.808}]</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.76)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.76}]</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -14757,12 +14801,12 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(18.527), 'mean_duration_us': np.float64(3.7054), 'median_duration_us': np.float64(3.712), 'std_dev_duration_us': np.float64(0.13307982566865645), 'min_duration_us': np.float64(3.488), 'max_duration_us': np.float64(3.871)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 18.527, 'mean_duration_us': 3.7054, 'median_duration_us': 3.712, 'std_dev_duration_us': 0.13307982566865645, 'min_duration_us': 3.488, 'max_duration_us': 3.871}]</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 7, 'mean_duration_us': np.float64(3.71)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 7, 'mean_duration_us': 3.71}]</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -14844,12 +14888,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(17.918), 'mean_duration_us': np.float64(3.5835999999999997), 'median_duration_us': np.float64(3.552), 'std_dev_duration_us': np.float64(0.049834124854360604), 'min_duration_us': np.float64(3.551), 'max_duration_us': np.float64(3.68)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 17.918, 'mean_duration_us': 3.5835999999999997, 'median_duration_us': 3.552, 'std_dev_duration_us': 0.049834124854360604, 'min_duration_us': 3.551, 'max_duration_us': 3.68}]</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -14931,12 +14975,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(17.44), 'mean_duration_us': np.float64(1.7440000000000002), 'median_duration_us': np.float64(1.7440000000000002), 'std_dev_duration_us': np.float64(0.9569284194755635), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 17.44, 'mean_duration_us': 1.7440000000000002, 'median_duration_us': 1.7440000000000002, 'std_dev_duration_us': 0.9569284194755635, 'min_duration_us': 0.768, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.74)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.74}]</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -15018,12 +15062,12 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(15.936), 'mean_duration_us': np.float64(3.1872), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.2268165778773677), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.488)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 15.936, 'mean_duration_us': 3.1872, 'median_duration_us': 3.104, 'std_dev_duration_us': 0.2268165778773677, 'min_duration_us': 2.944, 'max_duration_us': 3.488}]</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 3.19}]</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -15105,12 +15149,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.717999999999998), 'mean_duration_us': np.float64(2.9435999999999996), 'median_duration_us': np.float64(2.944), 'std_dev_duration_us': np.float64(0.0004898979485565817), 'min_duration_us': np.float64(2.943), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.717999999999998, 'mean_duration_us': 2.9435999999999996, 'median_duration_us': 2.944, 'std_dev_duration_us': 0.0004898979485565817, 'min_duration_us': 2.943, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.94)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.94}]</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -15192,12 +15236,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.657), 'mean_duration_us': np.float64(2.9314), 'median_duration_us': np.float64(2.944), 'std_dev_duration_us': np.float64(0.03232089107682529), 'min_duration_us': np.float64(2.881), 'max_duration_us': np.float64(2.976)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 14.657, 'mean_duration_us': 2.9314, 'median_duration_us': 2.944, 'std_dev_duration_us': 0.03232089107682529, 'min_duration_us': 2.881, 'max_duration_us': 2.976}]</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.93)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.93}]</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -15279,12 +15323,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.560000000000002), 'mean_duration_us': np.float64(2.9120000000000004), 'median_duration_us': np.float64(3.008), 'std_dev_duration_us': np.float64(0.21891368161903446), 'min_duration_us': np.float64(2.656), 'max_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 14.560000000000002, 'mean_duration_us': 2.9120000000000004, 'median_duration_us': 3.008, 'std_dev_duration_us': 0.21891368161903446, 'min_duration_us': 2.656, 'max_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.91)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.91}]</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -15366,12 +15410,12 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.495999999999999), 'mean_duration_us': np.float64(2.8991999999999996), 'median_duration_us': np.float64(2.912), 'std_dev_duration_us': np.float64(0.032633724886993856), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.495999999999999, 'mean_duration_us': 2.8991999999999996, 'median_duration_us': 2.912, 'std_dev_duration_us': 0.032633724886993856, 'min_duration_us': 2.848, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.9)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.9}]</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -15453,12 +15497,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.985), 'mean_duration_us': np.float64(2.7969999999999997), 'median_duration_us': np.float64(2.785), 'std_dev_duration_us': np.float64(0.015517731793016621), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.985, 'mean_duration_us': 2.7969999999999997, 'median_duration_us': 2.785, 'std_dev_duration_us': 0.015517731793016621, 'min_duration_us': 2.784, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.8)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 2.8}]</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -15540,12 +15584,12 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.472000000000001), 'mean_duration_us': np.float64(2.6944000000000004), 'median_duration_us': np.float64(2.752), 'std_dev_duration_us': np.float64(0.10398769157934018), 'min_duration_us': np.float64(2.528), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.472000000000001, 'mean_duration_us': 2.6944000000000004, 'median_duration_us': 2.752, 'std_dev_duration_us': 0.10398769157934018, 'min_duration_us': 2.528, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.69)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.69}]</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -15627,12 +15671,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.407000000000002), 'mean_duration_us': np.float64(2.6814000000000004), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.07142996570067763), 'min_duration_us': np.float64(2.623), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.407000000000002, 'mean_duration_us': 2.6814000000000004, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.07142996570067763, 'min_duration_us': 2.623, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.68)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.68}]</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -15714,12 +15758,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.345), 'mean_duration_us': np.float64(2.669), 'median_duration_us': np.float64(2.72), 'std_dev_duration_us': np.float64(0.08978641322605552), 'min_duration_us': np.float64(2.56), 'max_duration_us': np.float64(2.753)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.345, 'mean_duration_us': 2.669, 'median_duration_us': 2.72, 'std_dev_duration_us': 0.08978641322605552, 'min_duration_us': 2.56, 'max_duration_us': 2.753}]</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -15801,12 +15845,12 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(12.222999999999999), 'mean_duration_us': np.float64(2.4446), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.1469742834648294), 'min_duration_us': np.float64(2.303), 'max_duration_us': np.float64(2.624)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 12.222999999999999, 'mean_duration_us': 2.4446, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.1469742834648294, 'min_duration_us': 2.303, 'max_duration_us': 2.624}]</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.44)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.44}]</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -15888,12 +15932,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.04340691189200176), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.04340691189200176, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -15975,12 +16019,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0478932145507065), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.0478932145507065, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -16062,12 +16106,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.687), 'mean_duration_us': np.float64(2.1374), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.14060953026022097), 'min_duration_us': np.float64(1.952), 'max_duration_us': np.float64(2.272)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 10.687, 'mean_duration_us': 2.1374, 'median_duration_us': 2.208, 'std_dev_duration_us': 0.14060953026022097, 'min_duration_us': 1.952, 'max_duration_us': 2.272}]</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.14)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.14}]</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -16149,12 +16193,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.048), 'mean_duration_us': np.float64(2.0096), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.08442179813294667), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(2.112)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 10.048, 'mean_duration_us': 2.0096, 'median_duration_us': 2.016, 'std_dev_duration_us': 0.08442179813294667, 'min_duration_us': 1.856, 'max_duration_us': 2.112}]</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryF...', 'stream': 7, 'mean_duration_us': np.float64(2.01)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryF...', 'stream': 7, 'mean_duration_us': 2.01}]</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -16236,12 +16280,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(9.247), 'mean_duration_us': np.float64(1.8494), 'median_duration_us': np.float64(1.888), 'std_dev_duration_us': np.float64(0.12672426760490674), 'min_duration_us': np.float64(1.696), 'max_duration_us': np.float64(2.047)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 9.247, 'mean_duration_us': 1.8494, 'median_duration_us': 1.888, 'std_dev_duration_us': 0.12672426760490674, 'min_duration_us': 1.696, 'max_duration_us': 2.047}]</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': np.float64(1.85)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': 1.85}]</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -16323,12 +16367,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.896), 'mean_duration_us': np.float64(1.7792000000000001), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.025600000000000022), 'min_duration_us': np.float64(1.728), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.896, 'mean_duration_us': 1.7792000000000001, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.025600000000000022, 'min_duration_us': 1.728, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.78)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.78}]</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -16410,12 +16454,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.799), 'mean_duration_us': np.float64(1.7597999999999998), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.10100376230616363), 'min_duration_us': np.float64(1.632), 'max_duration_us': np.float64(1.888)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.799, 'mean_duration_us': 1.7597999999999998, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.10100376230616363, 'min_duration_us': 1.632, 'max_duration_us': 1.888}]</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.76)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.76}]</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -16497,12 +16541,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.769), 'mean_duration_us': np.float64(1.7538), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.0742762411542211), 'min_duration_us': np.float64(1.664), 'max_duration_us': np.float64(1.825)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.769, 'mean_duration_us': 1.7538, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.0742762411542211, 'min_duration_us': 1.664, 'max_duration_us': 1.825}]</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -16584,12 +16628,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.64), 'mean_duration_us': np.float64(1.7280000000000002), 'median_duration_us': np.float64(1.696), 'std_dev_duration_us': np.float64(0.10516273104099186), 'min_duration_us': np.float64(1.6), 'max_duration_us': np.float64(1.92)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.64, 'mean_duration_us': 1.7280000000000002, 'median_duration_us': 1.696, 'std_dev_duration_us': 0.10516273104099186, 'min_duration_us': 1.6, 'max_duration_us': 1.92}]</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.73)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.73}]</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -16671,12 +16715,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.479), 'mean_duration_us': np.float64(1.6957999999999998), 'median_duration_us': np.float64(1.696), 'std_dev_duration_us': np.float64(0.020556264252047336), 'min_duration_us': np.float64(1.663), 'max_duration_us': np.float64(1.728)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.479, 'mean_duration_us': 1.6957999999999998, 'median_duration_us': 1.696, 'std_dev_duration_us': 0.020556264252047336, 'min_duration_us': 1.663, 'max_duration_us': 1.728}]</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.7)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.7}]</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -16758,12 +16802,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.447), 'mean_duration_us': np.float64(1.6893999999999998), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.09808486121721335), 'min_duration_us': np.float64(1.599), 'max_duration_us': np.float64(1.824)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.447, 'mean_duration_us': 1.6893999999999998, 'median_duration_us': 1.632, 'std_dev_duration_us': 0.09808486121721335, 'min_duration_us': 1.599, 'max_duration_us': 1.824}]</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ex...', 'stream': 7, 'mean_duration_us': np.float64(1.69)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ex...', 'stream': 7, 'mean_duration_us': 1.69}]</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -16845,12 +16889,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.030999999999999), 'mean_duration_us': np.float64(1.6061999999999999), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.046786322787754936), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.663)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.030999999999999, 'mean_duration_us': 1.6061999999999999, 'median_duration_us': 1.632, 'std_dev_duration_us': 0.046786322787754936, 'min_duration_us': 1.536, 'max_duration_us': 1.663}]</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.61}]</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -16932,12 +16976,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(7.968), 'mean_duration_us': np.float64(0.7968), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.009600000000000008), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 7.968, 'mean_duration_us': 0.7968, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.009600000000000008, 'min_duration_us': 0.768, 'max_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -17019,12 +17063,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.872), 'mean_duration_us': np.float64(1.5744), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02394660727535325), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.6)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.872, 'mean_duration_us': 1.5744, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02394660727535325, 'min_duration_us': 1.536, 'max_duration_us': 1.6}]</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -17106,12 +17150,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.744), 'mean_duration_us': np.float64(1.5488), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.09185728060420688), 'min_duration_us': np.float64(1.408), 'max_duration_us': np.float64(1.632)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.744, 'mean_duration_us': 1.5488, 'median_duration_us': 1.6, 'std_dev_duration_us': 0.09185728060420688, 'min_duration_us': 1.408, 'max_duration_us': 1.632}]</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.55)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.55}]</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -17193,12 +17237,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.454000000000001), 'mean_duration_us': np.float64(1.4908000000000001), 'median_duration_us': np.float64(1.536), 'std_dev_duration_us': np.float64(0.0797932327957703), 'min_duration_us': np.float64(1.344), 'max_duration_us': np.float64(1.567)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.454000000000001, 'mean_duration_us': 1.4908000000000001, 'median_duration_us': 1.536, 'std_dev_duration_us': 0.0797932327957703, 'min_duration_us': 1.344, 'max_duration_us': 1.567}]</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.49}]</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -17280,12 +17324,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.424999999999999), 'mean_duration_us': np.float64(1.4849999999999999), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.025502941006872143), 'min_duration_us': np.float64(1.472), 'max_duration_us': np.float64(1.536)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.424999999999999, 'mean_duration_us': 1.4849999999999999, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.025502941006872143, 'min_duration_us': 1.472, 'max_duration_us': 1.536}]</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.48)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.48}]</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -17367,12 +17411,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.264999999999999), 'mean_duration_us': np.float64(1.4529999999999998), 'median_duration_us': np.float64(1.441), 'std_dev_duration_us': np.float64(0.015517731793016656), 'min_duration_us': np.float64(1.44), 'max_duration_us': np.float64(1.472)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.264999999999999, 'mean_duration_us': 1.4529999999999998, 'median_duration_us': 1.441, 'std_dev_duration_us': 0.015517731793016656, 'min_duration_us': 1.44, 'max_duration_us': 1.472}]</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.45)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.45}]</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -17454,12 +17498,12 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.134), 'mean_duration_us': np.float64(1.4268), 'median_duration_us': np.float64(1.375), 'std_dev_duration_us': np.float64(0.08990083425641834), 'min_duration_us': np.float64(1.343), 'max_duration_us': np.float64(1.536)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.134, 'mean_duration_us': 1.4268, 'median_duration_us': 1.375, 'std_dev_duration_us': 0.08990083425641834, 'min_duration_us': 1.343, 'max_duration_us': 1.536}]</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.43)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.43}]</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -17541,12 +17585,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.103999999999999), 'mean_duration_us': np.float64(1.4207999999999998), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.16639999999999996), 'min_duration_us': np.float64(1.248), 'max_duration_us': np.float64(1.696)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': 7.103999999999999, 'mean_duration_us': 1.4207999999999998, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.16639999999999996, 'min_duration_us': 1.248, 'max_duration_us': 1.696}]</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.42)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': 1.42}]</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -17628,12 +17672,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.040000000000001), 'mean_duration_us': np.float64(1.4080000000000001), 'median_duration_us': np.float64(1.344), 'std_dev_duration_us': np.float64(0.09706080568385983), 'min_duration_us': np.float64(1.312), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.040000000000001, 'mean_duration_us': 1.4080000000000001, 'median_duration_us': 1.344, 'std_dev_duration_us': 0.09706080568385983, 'min_duration_us': 1.312, 'max_duration_us': 1.568}]</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.41)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.41}]</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -17715,12 +17759,12 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.008999999999999), 'mean_duration_us': np.float64(1.4017999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08894132897590411), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.008999999999999, 'mean_duration_us': 1.4017999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08894132897590411, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -17802,12 +17846,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.008000000000001), 'mean_duration_us': np.float64(1.4016000000000002), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.09997119585160516), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.008000000000001, 'mean_duration_us': 1.4016000000000002, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.09997119585160516, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -17889,12 +17933,12 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.007999999999999), 'mean_duration_us': np.float64(1.4015999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08914168497397834), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.007999999999999, 'mean_duration_us': 1.4015999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08914168497397834, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -17976,12 +18020,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(6.687999999999999), 'mean_duration_us': np.float64(1.3375999999999997), 'median_duration_us': np.float64(1.408), 'std_dev_duration_us': np.float64(0.0868138237840034), 'min_duration_us': np.float64(1.216), 'max_duration_us': np.float64(1.408)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 6.687999999999999, 'mean_duration_us': 1.3375999999999997, 'median_duration_us': 1.408, 'std_dev_duration_us': 0.0868138237840034, 'min_duration_us': 1.216, 'max_duration_us': 1.408}]</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.34)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.34}]</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -18063,12 +18107,12 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(6.176), 'mean_duration_us': np.float64(1.2352), 'median_duration_us': np.float64(1.28), 'std_dev_duration_us': np.float64(0.08245823185104081), 'min_duration_us': np.float64(1.12), 'max_duration_us': np.float64(1.312)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': 6.176, 'mean_duration_us': 1.2352, 'median_duration_us': 1.28, 'std_dev_duration_us': 0.08245823185104081, 'min_duration_us': 1.12, 'max_duration_us': 1.312}]</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.24)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': 1.24}]</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -18150,12 +18194,12 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(5.984000000000001), 'mean_duration_us': np.float64(1.1968), 'median_duration_us': np.float64(1.12), 'std_dev_duration_us': np.float64(0.09406040612287402), 'min_duration_us': np.float64(1.12), 'max_duration_us': np.float64(1.312)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 5.984000000000001, 'mean_duration_us': 1.1968, 'median_duration_us': 1.12, 'std_dev_duration_us': 0.09406040612287402, 'min_duration_us': 1.12, 'max_duration_us': 1.312}]</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': np.float64(1.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': 1.2}]</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -18180,217 +18224,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>process_label</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>thread_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_duration_us</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_duration_us</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>std_duration_us</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>duration_us_median</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>duration_us_min</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>duration_us_max</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>perf_params</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>has_perf_model</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -18500,12 +18544,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(262422.467), 'mean_duration_us': np.float64(2186.8538916666666), 'median_duration_us': np.float64(2170.955), 'std_dev_duration_us': np.float64(52.45910857528236), 'min_duration_us': np.float64(2146.764), 'max_duration_us': np.float64(2395.817)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'count': 120, 'total_duration_us': 262422.467, 'mean_duration_us': 2186.8538916666666, 'median_duration_us': 2170.955, 'std_dev_duration_us': 52.45910857528236, 'min_duration_us': 2146.764, 'max_duration_us': 2395.817}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c...', 'stream': 7, 'mean_duration_us': np.float64(2186.85)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c...', 'stream': 7, 'mean_duration_us': 2186.85}]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr"/>
@@ -18653,12 +18697,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(130015.7), 'mean_duration_us': np.float64(1083.4641666666666), 'median_duration_us': np.float64(1082.965), 'std_dev_duration_us': np.float64(3.932529614919927), 'min_duration_us': np.float64(1075.574), 'max_duration_us': np.float64(1096.694)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 130015.7, 'mean_duration_us': 1083.4641666666666, 'median_duration_us': 1082.965, 'std_dev_duration_us': 3.932529614919927, 'min_duration_us': 1075.574, 'max_duration_us': 1096.694}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': np.float64(1083.46)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': 1083.46}]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -18810,12 +18854,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(99311.41), 'mean_duration_us': np.float64(827.5950833333334), 'median_duration_us': np.float64(826.9205), 'std_dev_duration_us': np.float64(2.9474507419783706), 'min_duration_us': np.float64(825.432), 'max_duration_us': np.float64(851.8)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 99311.41, 'mean_duration_us': 827.5950833333334, 'median_duration_us': 826.9205, 'std_dev_duration_us': 2.9474507419783706, 'min_duration_us': 825.432, 'max_duration_us': 851.8}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': np.float64(827.6)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': 827.6}]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -18967,12 +19011,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(449.6640000000001), 'mean_duration_us': np.float64(0.9368000000000002), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.14700191892171566), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.408)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(10035.521), 'mean_duration_us': np.float64(20.90733541666667), 'median_duration_us': np.float64(20.912), 'std_dev_duration_us': np.float64(0.2994497001373127), 'min_duration_us': np.float64(20.256), 'max_duration_us': np.float64(22.015)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': 449.6640000000001, 'mean_duration_us': 0.9368000000000002, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.14700191892171566, 'min_duration_us': 0.767, 'max_duration_us': 1.408}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': 10035.521, 'mean_duration_us': 20.90733541666667, 'median_duration_us': 20.912, 'std_dev_duration_us': 0.2994497001373127, 'min_duration_us': 20.256, 'max_duration_us': 22.015}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.94)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.91)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.94}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.91}]</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -19124,12 +19168,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8133.554), 'mean_duration_us': np.float64(1626.7108), 'median_duration_us': np.float64(347.196), 'std_dev_duration_us': np.float64(1579.6924965375256), 'min_duration_us': np.float64(325.565), 'max_duration_us': np.float64(3620.445)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 8133.554, 'mean_duration_us': 1626.7108, 'median_duration_us': 347.196, 'std_dev_duration_us': 1579.6924965375256, 'min_duration_us': 325.565, 'max_duration_us': 3620.445}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(1626.71)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 1626.71}]</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -19281,12 +19325,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(115.61200000000002), 'mean_duration_us': np.float64(0.9634333333333335), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.18370559478566667), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.6)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(7766.737), 'mean_duration_us': np.float64(64.72280833333333), 'median_duration_us': np.float64(64.639), 'std_dev_duration_us': np.float64(0.5570301951096441), 'min_duration_us': np.float64(63.711), 'max_duration_us': np.float64(65.951)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 115.61200000000002, 'mean_duration_us': 0.9634333333333335, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.18370559478566667, 'min_duration_us': 0.768, 'max_duration_us': 1.6}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 7766.737, 'mean_duration_us': 64.72280833333333, 'median_duration_us': 64.639, 'std_dev_duration_us': 0.5570301951096441, 'min_duration_us': 63.711, 'max_duration_us': 65.951}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.96)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(64.72)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.96}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 64.72}]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -19438,12 +19482,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(116.09), 'mean_duration_us': np.float64(0.9674166666666667), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.15527371441711854), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.568)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(6884.5689999999995), 'mean_duration_us': np.float64(57.37140833333333), 'median_duration_us': np.float64(57.344), 'std_dev_duration_us': np.float64(0.31250691981227396), 'min_duration_us': np.float64(56.639), 'max_duration_us': np.float64(58.048)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 116.09, 'mean_duration_us': 0.9674166666666667, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.15527371441711854, 'min_duration_us': 0.768, 'max_duration_us': 1.568}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 6884.5689999999995, 'mean_duration_us': 57.37140833333333, 'median_duration_us': 57.344, 'std_dev_duration_us': 0.31250691981227396, 'min_duration_us': 56.639, 'max_duration_us': 58.048}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.97)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(57.37)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.97}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 57.37}]</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -19595,12 +19639,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(5223.73), 'mean_duration_us': np.float64(43.53108333333333), 'median_duration_us': np.float64(43.3595), 'std_dev_duration_us': np.float64(0.6410638629566389), 'min_duration_us': np.float64(42.656), 'max_duration_us': np.float64(44.704)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 5223.73, 'mean_duration_us': 43.53108333333333, 'median_duration_us': 43.3595, 'std_dev_duration_us': 0.6410638629566389, 'min_duration_us': 42.656, 'max_duration_us': 44.704}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(43.53)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 43.53}]</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -19752,12 +19796,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': np.float64(5038.033), 'mean_duration_us': np.float64(13.994536111111112), 'median_duration_us': np.float64(13.152), 'std_dev_duration_us': np.float64(1.3500063184322875), 'min_duration_us': np.float64(12.736), 'max_duration_us': np.float64(16.288)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': 5038.033, 'mean_duration_us': 13.994536111111112, 'median_duration_us': 13.152, 'std_dev_duration_us': 1.3500063184322875, 'min_duration_us': 12.736, 'max_duration_us': 16.288}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.99}]</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -19909,12 +19953,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3988.498), 'mean_duration_us': np.float64(33.23748333333334), 'median_duration_us': np.float64(33.055), 'std_dev_duration_us': np.float64(0.39268874407375365), 'min_duration_us': np.float64(32.8), 'max_duration_us': np.float64(34.272)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3988.498, 'mean_duration_us': 33.23748333333334, 'median_duration_us': 33.055, 'std_dev_duration_us': 0.39268874407375365, 'min_duration_us': 32.8, 'max_duration_us': 34.272}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(33.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 33.24}]</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -20066,12 +20110,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': np.float64(3701.084), 'mean_duration_us': np.float64(14.804336), 'median_duration_us': np.float64(14.56), 'std_dev_duration_us': np.float64(0.5479889406767253), 'min_duration_us': np.float64(13.952), 'max_duration_us': np.float64(15.807)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 250, 'total_duration_us': 3701.084, 'mean_duration_us': 14.804336, 'median_duration_us': 14.56, 'std_dev_duration_us': 0.5479889406767253, 'min_duration_us': 13.952, 'max_duration_us': 15.807}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.8)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.8}]</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -20223,12 +20267,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3687.3240000000005), 'mean_duration_us': np.float64(30.727700000000006), 'median_duration_us': np.float64(30.591), 'std_dev_duration_us': np.float64(0.3214868737600341), 'min_duration_us': np.float64(30.336), 'max_duration_us': np.float64(31.711)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3687.3240000000005, 'mean_duration_us': 30.727700000000006, 'median_duration_us': 30.591, 'std_dev_duration_us': 0.3214868737600341, 'min_duration_us': 30.336, 'max_duration_us': 31.711}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(30.73)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 30.73}]</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -20380,12 +20424,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2338.761), 'mean_duration_us': np.float64(467.7522), 'median_duration_us': np.float64(464.252), 'std_dev_duration_us': np.float64(11.281809454161158), 'min_duration_us': np.float64(454.556), 'max_duration_us': np.float64(487.899)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2338.761, 'mean_duration_us': 467.7522, 'median_duration_us': 464.252, 'std_dev_duration_us': 11.281809454161158, 'min_duration_us': 454.556, 'max_duration_us': 487.899}]</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(467.75)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 467.75}]</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -20537,12 +20581,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2324.394), 'mean_duration_us': np.float64(464.87879999999996), 'median_duration_us': np.float64(472.188), 'std_dev_duration_us': np.float64(19.601893596282974), 'min_duration_us': np.float64(436.444), 'max_duration_us': np.float64(489.34)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2324.394, 'mean_duration_us': 464.87879999999996, 'median_duration_us': 472.188, 'std_dev_duration_us': 19.601893596282974, 'min_duration_us': 436.444, 'max_duration_us': 489.34}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(464.88)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 464.88}]</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -20694,12 +20738,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': np.float64(2317.353), 'mean_duration_us': np.float64(9.458583673469388), 'median_duration_us': np.float64(9.472), 'std_dev_duration_us': np.float64(0.3348456698101192), 'min_duration_us': np.float64(8.576), 'max_duration_us': np.float64(10.849)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': 2317.353, 'mean_duration_us': 9.458583673469388, 'median_duration_us': 9.472, 'std_dev_duration_us': 0.3348456698101192, 'min_duration_us': 8.576, 'max_duration_us': 10.849}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(9.46)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 9.46}]</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -20851,12 +20895,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(1873.8329999999999), 'mean_duration_us': np.float64(15.615274999999999), 'median_duration_us': np.float64(15.584), 'std_dev_duration_us': np.float64(0.1854254999768552), 'min_duration_us': np.float64(15.264), 'max_duration_us': np.float64(16.384)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 1873.8329999999999, 'mean_duration_us': 15.615274999999999, 'median_duration_us': 15.584, 'std_dev_duration_us': 0.1854254999768552, 'min_duration_us': 15.264, 'max_duration_us': 16.384}]</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(15.62)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 15.62}]</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -21008,12 +21052,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(1627.952), 'mean_duration_us': np.float64(325.5904), 'median_duration_us': np.float64(333.501), 'std_dev_duration_us': np.float64(11.368233417730304), 'min_duration_us': np.float64(304.989), 'max_duration_us': np.float64(334.205)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 1627.952, 'mean_duration_us': 325.5904, 'median_duration_us': 333.501, 'std_dev_duration_us': 11.368233417730304, 'min_duration_us': 304.989, 'max_duration_us': 334.205}]</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(325.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 325.59}]</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -21165,12 +21209,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': np.float64(1579.851), 'mean_duration_us': np.float64(6.5827125), 'median_duration_us': np.float64(6.592), 'std_dev_duration_us': np.float64(0.13116311667951205), 'min_duration_us': np.float64(6.303), 'max_duration_us': np.float64(6.975)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': 1579.851, 'mean_duration_us': 6.5827125, 'median_duration_us': 6.592, 'std_dev_duration_us': 0.13116311667951205, 'min_duration_us': 6.303, 'max_duration_us': 6.975}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.58)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.58}]</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -21322,12 +21366,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(28.127000000000002), 'mean_duration_us': np.float64(5.625400000000001), 'median_duration_us': np.float64(5.664), 'std_dev_duration_us': np.float64(0.08941498755801505), 'min_duration_us': np.float64(5.503), 'max_duration_us': np.float64(5.728)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(222.207), 'mean_duration_us': np.float64(44.4414), 'median_duration_us': np.float64(44.384), 'std_dev_duration_us': np.float64(0.1792647204555328), 'min_duration_us': np.float64(44.224), 'max_duration_us': np.float64(44.768)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.85), 'mean_duration_us': np.float64(2.17), 'median_duration_us': np.float64(2.176), 'std_dev_duration_us': np.float64(0.013007690033207267), 'min_duration_us': np.float64(2.144), 'max_duration_us': np.float64(2.177)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(58.303000000000004), 'mean_duration_us': np.float64(11.6606), 'median_duration_us': np.float64(11.679), 'std_dev_duration_us': np.float64(0.15088485676170435), 'min_duration_us': np.float64(11.424), 'max_duration_us': np.float64(11.872)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(982.9660000000001), 'mean_duration_us': np.float64(196.59320000000002), 'median_duration_us': np.float64(196.542), 'std_dev_duration_us': np.float64(0.4292092263686784), 'min_duration_us': np.float64(195.966), 'max_duration_us': np.float64(197.245)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(48.35), 'mean_duration_us': np.float64(9.67), 'median_duration_us': np.float64(9.663), 'std_dev_duration_us': np.float64(0.0547539952880155), 'min_duration_us': np.float64(9.6), 'max_duration_us': np.float64(9.759)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 28.127000000000002, 'mean_duration_us': 5.625400000000001, 'median_duration_us': 5.664, 'std_dev_duration_us': 0.08941498755801505, 'min_duration_us': 5.503, 'max_duration_us': 5.728}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 222.207, 'mean_duration_us': 44.4414, 'median_duration_us': 44.384, 'std_dev_duration_us': 0.1792647204555328, 'min_duration_us': 44.224, 'max_duration_us': 44.768}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 10.85, 'mean_duration_us': 2.17, 'median_duration_us': 2.176, 'std_dev_duration_us': 0.013007690033207267, 'min_duration_us': 2.144, 'max_duration_us': 2.177}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 58.303000000000004, 'mean_duration_us': 11.6606, 'median_duration_us': 11.679, 'std_dev_duration_us': 0.15088485676170435, 'min_duration_us': 11.424, 'max_duration_us': 11.872}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 982.9660000000001, 'mean_duration_us': 196.59320000000002, 'median_duration_us': 196.542, 'std_dev_duration_us': 0.4292092263686784, 'min_duration_us': 195.966, 'max_duration_us': 197.245}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 48.35, 'mean_duration_us': 9.67, 'median_duration_us': 9.663, 'std_dev_duration_us': 0.0547539952880155, 'min_duration_us': 9.6, 'max_duration_us': 9.759}]</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(5.63)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(44.44)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.17)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(11.66)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(196.59)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(9.67)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 5.63}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 44.44}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 2.17}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 11.66}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': 196.59}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 9.67}]</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -21479,12 +21523,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(934.809), 'mean_duration_us': np.float64(7.790075), 'median_duration_us': np.float64(7.776), 'std_dev_duration_us': np.float64(0.06863528763204346), 'min_duration_us': np.float64(7.711), 'max_duration_us': np.float64(8.032)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 934.809, 'mean_duration_us': 7.790075, 'median_duration_us': 7.776, 'std_dev_duration_us': 0.06863528763204346, 'min_duration_us': 7.711, 'max_duration_us': 8.032}]</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(7.79)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 7.79}]</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -21636,12 +21680,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(385.4959999999999), 'mean_duration_us': np.float64(6.424933333333332), 'median_duration_us': np.float64(6.336), 'std_dev_duration_us': np.float64(0.19279919317489072), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(6.912)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(140.35000000000002), 'mean_duration_us': np.float64(2.339166666666667), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.037292164801142315), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.496)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 385.4959999999999, 'mean_duration_us': 6.424933333333332, 'median_duration_us': 6.336, 'std_dev_duration_us': 0.19279919317489072, 'min_duration_us': 6.239, 'max_duration_us': 6.912}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': 140.35000000000002, 'mean_duration_us': 2.339166666666667, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.037292164801142315, 'min_duration_us': 2.272, 'max_duration_us': 2.496}]</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.42)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.42}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 2.34}]</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -21793,12 +21837,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': np.float64(457.9199999999999), 'mean_duration_us': np.float64(2.5439999999999996), 'median_duration_us': np.float64(2.4645), 'std_dev_duration_us': np.float64(0.22104903930525865), 'min_duration_us': np.float64(2.24), 'max_duration_us': np.float64(3.232)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': 457.9199999999999, 'mean_duration_us': 2.5439999999999996, 'median_duration_us': 2.4645, 'std_dev_duration_us': 0.22104903930525865, 'min_duration_us': 2.24, 'max_duration_us': 3.232}]</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.54}]</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -21950,12 +21994,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(451.14099999999996), 'mean_duration_us': np.float64(3.6091279999999997), 'median_duration_us': np.float64(3.584), 'std_dev_duration_us': np.float64(0.16081094370719926), 'min_duration_us': np.float64(3.328), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 125, 'total_duration_us': 451.14099999999996, 'mean_duration_us': 3.6091279999999997, 'median_duration_us': 3.584, 'std_dev_duration_us': 0.16081094370719926, 'min_duration_us': 3.328, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(3.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 3.61}]</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -22107,12 +22151,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(17.248), 'mean_duration_us': np.float64(0.8624), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.13365305832639968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.248)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(414.7149999999999), 'mean_duration_us': np.float64(20.735749999999996), 'median_duration_us': np.float64(20.768), 'std_dev_duration_us': np.float64(0.42032010123238245), 'min_duration_us': np.float64(19.936), 'max_duration_us': np.float64(21.279)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': 17.248, 'mean_duration_us': 0.8624, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.13365305832639968, 'min_duration_us': 0.768, 'max_duration_us': 1.248}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': 414.7149999999999, 'mean_duration_us': 20.735749999999996, 'median_duration_us': 20.768, 'std_dev_duration_us': 0.42032010123238245, 'min_duration_us': 19.936, 'max_duration_us': 21.279}]</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.86)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.74)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.86}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.74}]</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -22264,12 +22308,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(422.845), 'mean_duration_us': np.float64(7.047416666666667), 'median_duration_us': np.float64(6.976), 'std_dev_duration_us': np.float64(0.17790056133194818), 'min_duration_us': np.float64(6.752), 'max_duration_us': np.float64(7.52)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 422.845, 'mean_duration_us': 7.047416666666667, 'median_duration_us': 6.976, 'std_dev_duration_us': 0.17790056133194818, 'min_duration_us': 6.752, 'max_duration_us': 7.52}]</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(7.05)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 7.05}]</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -22421,12 +22465,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(287.13699999999994), 'mean_duration_us': np.float64(2.392808333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.24387456802740948), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.913)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 287.13699999999994, 'mean_duration_us': 2.392808333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.24387456802740948, 'min_duration_us': 1.984, 'max_duration_us': 2.913}]</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.39)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.39}]</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -22548,12 +22592,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(219.806), 'mean_duration_us': np.float64(43.961200000000005), 'median_duration_us': np.float64(43.712), 'std_dev_duration_us': np.float64(0.48020553932665044), 'min_duration_us': np.float64(43.551), 'max_duration_us': np.float64(44.799)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 5, 'total_duration_us': 219.806, 'mean_duration_us': 43.961200000000005, 'median_duration_us': 43.712, 'std_dev_duration_us': 0.48020553932665044, 'min_duration_us': 43.551, 'max_duration_us': 44.799}]</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(43.96)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': 43.96}]</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr"/>
@@ -22671,12 +22715,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(195.071), 'mean_duration_us': np.float64(39.0142), 'median_duration_us': np.float64(39.072), 'std_dev_duration_us': np.float64(0.2134070289376613), 'min_duration_us': np.float64(38.624), 'max_duration_us': np.float64(39.231)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 195.071, 'mean_duration_us': 39.0142, 'median_duration_us': 39.072, 'std_dev_duration_us': 0.2134070289376613, 'min_duration_us': 38.624, 'max_duration_us': 39.231}]</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(39.01)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 39.01}]</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr"/>
@@ -22824,12 +22868,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(187.747), 'mean_duration_us': np.float64(1.5019760000000002), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.09206636423797784), 'min_duration_us': np.float64(1.344), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': 187.747, 'mean_duration_us': 1.5019760000000002, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.09206636423797784, 'min_duration_us': 1.344, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.5}]</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -22981,12 +23025,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(185.69699999999997), 'mean_duration_us': np.float64(3.0949499999999994), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.04453478977159322), 'min_duration_us': np.float64(3.008), 'max_duration_us': np.float64(3.168)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 185.69699999999997, 'mean_duration_us': 3.0949499999999994, 'median_duration_us': 3.104, 'std_dev_duration_us': 0.04453478977159322, 'min_duration_us': 3.008, 'max_duration_us': 3.168}]</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(3.09)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 3.09}]</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -23108,12 +23152,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(176.76800000000006), 'mean_duration_us': np.float64(8.838400000000004), 'median_duration_us': np.float64(8.832), 'std_dev_duration_us': np.float64(0.06681796165702758), 'min_duration_us': np.float64(8.704), 'max_duration_us': np.float64(8.992)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 20, 'total_duration_us': 176.76800000000006, 'mean_duration_us': 8.838400000000004, 'median_duration_us': 8.832, 'std_dev_duration_us': 0.06681796165702758, 'min_duration_us': 8.704, 'max_duration_us': 8.992}]</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(8.84)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': 8.84}]</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr"/>
@@ -23261,12 +23305,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(167.428), 'mean_duration_us': np.float64(2.7904666666666667), 'median_duration_us': np.float64(2.816), 'std_dev_duration_us': np.float64(0.037250264726874344), 'min_duration_us': np.float64(2.72), 'max_duration_us': np.float64(2.88)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 167.428, 'mean_duration_us': 2.7904666666666667, 'median_duration_us': 2.816, 'std_dev_duration_us': 0.037250264726874344, 'min_duration_us': 2.72, 'max_duration_us': 2.88}]</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(2.79)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 2.79}]</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -23418,12 +23462,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(163.17200000000005), 'mean_duration_us': np.float64(2.719533333333334), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.14011381881250043), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': 163.17200000000005, 'mean_duration_us': 2.719533333333334, 'median_duration_us': 2.784, 'std_dev_duration_us': 0.14011381881250043, 'min_duration_us': 2.527, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -23575,12 +23619,12 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(35.168), 'mean_duration_us': np.float64(2.344533333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.10418372660300108), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.56)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(83.104), 'mean_duration_us': np.float64(5.540266666666667), 'median_duration_us': np.float64(5.376), 'std_dev_duration_us': np.float64(0.32818683025916123), 'min_duration_us': np.float64(5.152), 'max_duration_us': np.float64(6.176)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': 35.168, 'mean_duration_us': 2.344533333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.10418372660300108, 'min_duration_us': 2.176, 'max_duration_us': 2.56}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': 83.104, 'mean_duration_us': 5.540266666666667, 'median_duration_us': 5.376, 'std_dev_duration_us': 0.32818683025916123, 'min_duration_us': 5.152, 'max_duration_us': 6.176}]</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(5.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.34}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 5.54}]</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -23702,12 +23746,12 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(115.74799999999999), 'mean_duration_us': np.float64(1.9291333333333331), 'median_duration_us': np.float64(1.857), 'std_dev_duration_us': np.float64(0.09073284349610612), 'min_duration_us': np.float64(1.824), 'max_duration_us': np.float64(2.049)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'count': 60, 'total_duration_us': 115.74799999999999, 'mean_duration_us': 1.9291333333333331, 'median_duration_us': 1.857, 'std_dev_duration_us': 0.09073284349610612, 'min_duration_us': 1.824, 'max_duration_us': 2.049}]</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 7, 'mean_duration_us': np.float64(1.93)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 7, 'mean_duration_us': 1.93}]</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr"/>
@@ -23855,12 +23899,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(105.02100000000002), 'mean_duration_us': np.float64(1.7503500000000003), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.021235838418422137), 'min_duration_us': np.float64(1.696), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 105.02100000000002, 'mean_duration_us': 1.7503500000000003, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.021235838418422137, 'min_duration_us': 1.696, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -24012,12 +24056,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(94.07899999999998), 'mean_duration_us': np.float64(1.567983333333333), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02925092116308288), 'min_duration_us': np.float64(1.535), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 94.07899999999998, 'mean_duration_us': 1.567983333333333, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02925092116308288, 'min_duration_us': 1.535, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -24169,12 +24213,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(89.14699999999999), 'mean_duration_us': np.float64(1.4857833333333332), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.016880058912482752), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.535)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 89.14699999999999, 'mean_duration_us': 1.4857833333333332, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.016880058912482752, 'min_duration_us': 1.471, 'max_duration_us': 1.535}]</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.49}]</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -24326,12 +24370,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(86.78200000000001), 'mean_duration_us': np.float64(17.3564), 'median_duration_us': np.float64(17.376), 'std_dev_duration_us': np.float64(0.07209049868047837), 'min_duration_us': np.float64(17.215), 'max_duration_us': np.float64(17.408)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': 86.78200000000001, 'mean_duration_us': 17.3564, 'median_duration_us': 17.376, 'std_dev_duration_us': 0.07209049868047837, 'min_duration_us': 17.215, 'max_duration_us': 17.408}]</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(17.36)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': 17.36}]</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -24483,12 +24527,12 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(86.49500000000002), 'mean_duration_us': np.float64(1.4415833333333337), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.10003121040733015), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 86.49500000000002, 'mean_duration_us': 1.4415833333333337, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.10003121040733015, 'min_duration_us': 1.28, 'max_duration_us': 1.568}]</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.44)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.44}]</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -24640,12 +24684,12 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(70.463), 'mean_duration_us': np.float64(14.0926), 'median_duration_us': np.float64(14.079), 'std_dev_duration_us': np.float64(0.1321144957981524), 'min_duration_us': np.float64(13.92), 'max_duration_us': np.float64(14.272)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 70.463, 'mean_duration_us': 14.0926, 'median_duration_us': 14.079, 'std_dev_duration_us': 0.1321144957981524, 'min_duration_us': 13.92, 'max_duration_us': 14.272}]</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(14.09)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 14.09}]</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -24797,12 +24841,12 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(65.407), 'mean_duration_us': np.float64(13.081399999999999), 'median_duration_us': np.float64(13.088), 'std_dev_duration_us': np.float64(0.058854396607220374), 'min_duration_us': np.float64(13.023), 'max_duration_us': np.float64(13.184)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 65.407, 'mean_duration_us': 13.081399999999999, 'median_duration_us': 13.088, 'std_dev_duration_us': 0.058854396607220374, 'min_duration_us': 13.023, 'max_duration_us': 13.184}]</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.08)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.08}]</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -24954,12 +24998,12 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(57.631), 'mean_duration_us': np.float64(11.5262), 'median_duration_us': np.float64(11.552), 'std_dev_duration_us': np.float64(0.0889413289759043), 'min_duration_us': np.float64(11.392), 'max_duration_us': np.float64(11.616)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 57.631, 'mean_duration_us': 11.5262, 'median_duration_us': 11.552, 'std_dev_duration_us': 0.0889413289759043, 'min_duration_us': 11.392, 'max_duration_us': 11.616}]</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(11.53)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 11.53}]</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
@@ -25111,12 +25155,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(56.54299999999999), 'mean_duration_us': np.float64(11.308599999999998), 'median_duration_us': np.float64(11.296), 'std_dev_duration_us': np.float64(0.10403768547983014), 'min_duration_us': np.float64(11.168), 'max_duration_us': np.float64(11.487)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 56.54299999999999, 'mean_duration_us': 11.308599999999998, 'median_duration_us': 11.296, 'std_dev_duration_us': 0.10403768547983014, 'min_duration_us': 11.168, 'max_duration_us': 11.487}]</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(11.31)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 11.31}]</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -25268,12 +25312,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(31.743), 'mean_duration_us': np.float64(3.1742999999999997), 'median_duration_us': np.float64(3.216), 'std_dev_duration_us': np.float64(0.22374005005809758), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(3.551)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 10, 'total_duration_us': 31.743, 'mean_duration_us': 3.1742999999999997, 'median_duration_us': 3.216, 'std_dev_duration_us': 0.22374005005809758, 'min_duration_us': 2.848, 'max_duration_us': 3.551}]</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.17)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 3.17}]</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -25395,12 +25439,12 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(28.159999999999997), 'mean_duration_us': np.float64(5.632), 'median_duration_us': np.float64(5.792), 'std_dev_duration_us': np.float64(0.2638787600395301), 'min_duration_us': np.float64(5.28), 'max_duration_us': np.float64(5.888)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 28.159999999999997, 'mean_duration_us': 5.632, 'median_duration_us': 5.792, 'std_dev_duration_us': 0.2638787600395301, 'min_duration_us': 5.28, 'max_duration_us': 5.888}]</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(5.63)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 5.63}]</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr"/>
@@ -25548,12 +25592,12 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(26.686999999999998), 'mean_duration_us': np.float64(2.6687), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.20862696374150683), 'min_duration_us': np.float64(2.335), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': 26.686999999999998, 'mean_duration_us': 2.6687, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.20862696374150683, 'min_duration_us': 2.335, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
@@ -25675,12 +25719,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(26.463), 'mean_duration_us': np.float64(5.2926), 'median_duration_us': np.float64(5.216), 'std_dev_duration_us': np.float64(0.19653355947522047), 'min_duration_us': np.float64(5.088), 'max_duration_us': np.float64(5.599)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 7, 'count': 5, 'total_duration_us': 26.463, 'mean_duration_us': 5.2926, 'median_duration_us': 5.216, 'std_dev_duration_us': 0.19653355947522047, 'min_duration_us': 5.088, 'max_duration_us': 5.599}]</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(5.29)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 7, 'mean_duration_us': 5.29}]</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr"/>
@@ -25828,12 +25872,12 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(24.704), 'mean_duration_us': np.float64(4.9408), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.05935115837117255), 'min_duration_us': np.float64(4.832), 'max_duration_us': np.float64(4.992)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 24.704, 'mean_duration_us': 4.9408, 'median_duration_us': 4.96, 'std_dev_duration_us': 0.05935115837117255, 'min_duration_us': 4.832, 'max_duration_us': 4.992}]</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(4.94)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 4.94}]</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -25985,12 +26029,12 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(23.615000000000002), 'mean_duration_us': np.float64(4.723000000000001), 'median_duration_us': np.float64(4.704), 'std_dev_duration_us': np.float64(0.06861486719363401), 'min_duration_us': np.float64(4.64), 'max_duration_us': np.float64(4.831)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': 23.615000000000002, 'mean_duration_us': 4.723000000000001, 'median_duration_us': 4.704, 'std_dev_duration_us': 0.06861486719363401, 'min_duration_us': 4.64, 'max_duration_us': 4.831}]</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(4.72)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 4.72}]</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -26142,12 +26186,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.143), 'mean_duration_us': np.float64(2.0286), 'median_duration_us': np.float64(2.047), 'std_dev_duration_us': np.float64(0.02545270123189289), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.048)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.183000000000002), 'mean_duration_us': np.float64(2.6366000000000005), 'median_duration_us': np.float64(2.688), 'std_dev_duration_us': np.float64(0.08984341934721768), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 10.143, 'mean_duration_us': 2.0286, 'median_duration_us': 2.047, 'std_dev_duration_us': 0.02545270123189289, 'min_duration_us': 1.984, 'max_duration_us': 2.048}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.183000000000002, 'mean_duration_us': 2.6366000000000005, 'median_duration_us': 2.688, 'std_dev_duration_us': 0.08984341934721768, 'min_duration_us': 2.527, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': np.float64(2.03)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': np.float64(2.64)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': 2.03}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': 2.64}]</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -26269,12 +26313,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(22.176000000000002), 'mean_duration_us': np.float64(4.4352), 'median_duration_us': np.float64(4.256), 'std_dev_duration_us': np.float64(0.26400560600108475), 'min_duration_us': np.float64(4.192), 'max_duration_us': np.float64(4.832)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 22.176000000000002, 'mean_duration_us': 4.4352, 'median_duration_us': 4.256, 'std_dev_duration_us': 0.26400560600108475, 'min_duration_us': 4.192, 'max_duration_us': 4.832}]</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 7, 'mean_duration_us': np.float64(4.44)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 7, 'mean_duration_us': 4.44}]</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr"/>
@@ -26422,12 +26466,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(22.144000000000002), 'mean_duration_us': np.float64(4.428800000000001), 'median_duration_us': np.float64(4.416), 'std_dev_duration_us': np.float64(0.09621309682158638), 'min_duration_us': np.float64(4.32), 'max_duration_us': np.float64(4.608)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 22.144000000000002, 'mean_duration_us': 4.428800000000001, 'median_duration_us': 4.416, 'std_dev_duration_us': 0.09621309682158638, 'min_duration_us': 4.32, 'max_duration_us': 4.608}]</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': np.float64(4.43)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': 4.43}]</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -26579,12 +26623,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.255), 'mean_duration_us': np.float64(4.051), 'median_duration_us': np.float64(4.032), 'std_dev_duration_us': np.float64(0.02550294100687212), 'min_duration_us': np.float64(4.032), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 20.255, 'mean_duration_us': 4.051, 'median_duration_us': 4.032, 'std_dev_duration_us': 0.02550294100687212, 'min_duration_us': 4.032, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(4.05)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 4.05}]</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -26736,12 +26780,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.128), 'mean_duration_us': np.float64(4.0256), 'median_duration_us': np.float64(4.0), 'std_dev_duration_us': np.float64(0.13636656481704024), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(4.224)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 20.128, 'mean_duration_us': 4.0256, 'median_duration_us': 4.0, 'std_dev_duration_us': 0.13636656481704024, 'min_duration_us': 3.808, 'max_duration_us': 4.224}]</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.03)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': 4.03}]</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -26893,12 +26937,12 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(18.784), 'mean_duration_us': np.float64(3.7567999999999997), 'median_duration_us': np.float64(3.744), 'std_dev_duration_us': np.float64(0.03263372488699366), 'min_duration_us': np.float64(3.712), 'max_duration_us': np.float64(3.808)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 18.784, 'mean_duration_us': 3.7567999999999997, 'median_duration_us': 3.744, 'std_dev_duration_us': 0.03263372488699366, 'min_duration_us': 3.712, 'max_duration_us': 3.808}]</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.76)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.76}]</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
@@ -27020,12 +27064,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(18.527), 'mean_duration_us': np.float64(3.7054), 'median_duration_us': np.float64(3.712), 'std_dev_duration_us': np.float64(0.13307982566865645), 'min_duration_us': np.float64(3.488), 'max_duration_us': np.float64(3.871)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 18.527, 'mean_duration_us': 3.7054, 'median_duration_us': 3.712, 'std_dev_duration_us': 0.13307982566865645, 'min_duration_us': 3.488, 'max_duration_us': 3.871}]</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 7, 'mean_duration_us': np.float64(3.71)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 7, 'mean_duration_us': 3.71}]</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr"/>
@@ -27173,12 +27217,12 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(17.918), 'mean_duration_us': np.float64(3.5835999999999997), 'median_duration_us': np.float64(3.552), 'std_dev_duration_us': np.float64(0.049834124854360604), 'min_duration_us': np.float64(3.551), 'max_duration_us': np.float64(3.68)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 17.918, 'mean_duration_us': 3.5835999999999997, 'median_duration_us': 3.552, 'std_dev_duration_us': 0.049834124854360604, 'min_duration_us': 3.551, 'max_duration_us': 3.68}]</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
@@ -27312,12 +27356,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(17.44), 'mean_duration_us': np.float64(1.7440000000000002), 'median_duration_us': np.float64(1.7440000000000002), 'std_dev_duration_us': np.float64(0.9569284194755635), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 17.44, 'mean_duration_us': 1.7440000000000002, 'median_duration_us': 1.7440000000000002, 'std_dev_duration_us': 0.9569284194755635, 'min_duration_us': 0.768, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.74)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.74}]</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
@@ -27469,12 +27513,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(15.936), 'mean_duration_us': np.float64(3.1872), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.2268165778773677), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.488)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 15.936, 'mean_duration_us': 3.1872, 'median_duration_us': 3.104, 'std_dev_duration_us': 0.2268165778773677, 'min_duration_us': 2.944, 'max_duration_us': 3.488}]</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(3.19)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': 3.19}]</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -27626,12 +27670,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.717999999999998), 'mean_duration_us': np.float64(2.9435999999999996), 'median_duration_us': np.float64(2.944), 'std_dev_duration_us': np.float64(0.0004898979485565817), 'min_duration_us': np.float64(2.943), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.717999999999998, 'mean_duration_us': 2.9435999999999996, 'median_duration_us': 2.944, 'std_dev_duration_us': 0.0004898979485565817, 'min_duration_us': 2.943, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.94)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.94}]</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -27753,12 +27797,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.657), 'mean_duration_us': np.float64(2.9314), 'median_duration_us': np.float64(2.944), 'std_dev_duration_us': np.float64(0.03232089107682529), 'min_duration_us': np.float64(2.881), 'max_duration_us': np.float64(2.976)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 14.657, 'mean_duration_us': 2.9314, 'median_duration_us': 2.944, 'std_dev_duration_us': 0.03232089107682529, 'min_duration_us': 2.881, 'max_duration_us': 2.976}]</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.93)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.93}]</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr"/>
@@ -27906,12 +27950,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.560000000000002), 'mean_duration_us': np.float64(2.9120000000000004), 'median_duration_us': np.float64(3.008), 'std_dev_duration_us': np.float64(0.21891368161903446), 'min_duration_us': np.float64(2.656), 'max_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 14.560000000000002, 'mean_duration_us': 2.9120000000000004, 'median_duration_us': 3.008, 'std_dev_duration_us': 0.21891368161903446, 'min_duration_us': 2.656, 'max_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.91)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.91}]</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -28063,12 +28107,12 @@
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.495999999999999), 'mean_duration_us': np.float64(2.8991999999999996), 'median_duration_us': np.float64(2.912), 'std_dev_duration_us': np.float64(0.032633724886993856), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.495999999999999, 'mean_duration_us': 2.8991999999999996, 'median_duration_us': 2.912, 'std_dev_duration_us': 0.032633724886993856, 'min_duration_us': 2.848, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.9)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.9}]</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -28220,12 +28264,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.985), 'mean_duration_us': np.float64(2.7969999999999997), 'median_duration_us': np.float64(2.785), 'std_dev_duration_us': np.float64(0.015517731793016621), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.985, 'mean_duration_us': 2.7969999999999997, 'median_duration_us': 2.785, 'std_dev_duration_us': 0.015517731793016621, 'min_duration_us': 2.784, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.8)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 2.8}]</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
@@ -28377,12 +28421,12 @@
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.472000000000001), 'mean_duration_us': np.float64(2.6944000000000004), 'median_duration_us': np.float64(2.752), 'std_dev_duration_us': np.float64(0.10398769157934018), 'min_duration_us': np.float64(2.528), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.472000000000001, 'mean_duration_us': 2.6944000000000004, 'median_duration_us': 2.752, 'std_dev_duration_us': 0.10398769157934018, 'min_duration_us': 2.528, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.69)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.69}]</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
@@ -28534,12 +28578,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.407000000000002), 'mean_duration_us': np.float64(2.6814000000000004), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.07142996570067763), 'min_duration_us': np.float64(2.623), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.407000000000002, 'mean_duration_us': 2.6814000000000004, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.07142996570067763, 'min_duration_us': 2.623, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.68)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.68}]</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
@@ -28691,12 +28735,12 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.345), 'mean_duration_us': np.float64(2.669), 'median_duration_us': np.float64(2.72), 'std_dev_duration_us': np.float64(0.08978641322605552), 'min_duration_us': np.float64(2.56), 'max_duration_us': np.float64(2.753)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.345, 'mean_duration_us': 2.669, 'median_duration_us': 2.72, 'std_dev_duration_us': 0.08978641322605552, 'min_duration_us': 2.56, 'max_duration_us': 2.753}]</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
@@ -28848,12 +28892,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(12.222999999999999), 'mean_duration_us': np.float64(2.4446), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.1469742834648294), 'min_duration_us': np.float64(2.303), 'max_duration_us': np.float64(2.624)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 12.222999999999999, 'mean_duration_us': 2.4446, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.1469742834648294, 'min_duration_us': 2.303, 'max_duration_us': 2.624}]</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.44)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.44}]</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
@@ -29005,12 +29049,12 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.04340691189200176), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.04340691189200176, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
@@ -29162,12 +29206,12 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0478932145507065), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.0478932145507065, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -29289,12 +29333,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.687), 'mean_duration_us': np.float64(2.1374), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.14060953026022097), 'min_duration_us': np.float64(1.952), 'max_duration_us': np.float64(2.272)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 10.687, 'mean_duration_us': 2.1374, 'median_duration_us': 2.208, 'std_dev_duration_us': 0.14060953026022097, 'min_duration_us': 1.952, 'max_duration_us': 2.272}]</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.14)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.14}]</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr"/>
@@ -29412,12 +29456,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.048), 'mean_duration_us': np.float64(2.0096), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.08442179813294667), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(2.112)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 10.048, 'mean_duration_us': 2.0096, 'median_duration_us': 2.016, 'std_dev_duration_us': 0.08442179813294667, 'min_duration_us': 1.856, 'max_duration_us': 2.112}]</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryF...', 'stream': 7, 'mean_duration_us': np.float64(2.01)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::AUnaryF...', 'stream': 7, 'mean_duration_us': 2.01}]</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr"/>
@@ -29535,12 +29579,12 @@
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(9.247), 'mean_duration_us': np.float64(1.8494), 'median_duration_us': np.float64(1.888), 'std_dev_duration_us': np.float64(0.12672426760490674), 'min_duration_us': np.float64(1.696), 'max_duration_us': np.float64(2.047)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 9.247, 'mean_duration_us': 1.8494, 'median_duration_us': 1.888, 'std_dev_duration_us': 0.12672426760490674, 'min_duration_us': 1.696, 'max_duration_us': 2.047}]</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': np.float64(1.85)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': 1.85}]</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr"/>
@@ -29688,12 +29732,12 @@
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.896), 'mean_duration_us': np.float64(1.7792000000000001), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.025600000000000022), 'min_duration_us': np.float64(1.728), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.896, 'mean_duration_us': 1.7792000000000001, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.025600000000000022, 'min_duration_us': 1.728, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.78)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.78}]</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -29845,12 +29889,12 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.799), 'mean_duration_us': np.float64(1.7597999999999998), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.10100376230616363), 'min_duration_us': np.float64(1.632), 'max_duration_us': np.float64(1.888)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.799, 'mean_duration_us': 1.7597999999999998, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.10100376230616363, 'min_duration_us': 1.632, 'max_duration_us': 1.888}]</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.76)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.76}]</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -29984,12 +30028,12 @@
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.769), 'mean_duration_us': np.float64(1.7538), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.0742762411542211), 'min_duration_us': np.float64(1.664), 'max_duration_us': np.float64(1.825)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.769, 'mean_duration_us': 1.7538, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.0742762411542211, 'min_duration_us': 1.664, 'max_duration_us': 1.825}]</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
@@ -30123,12 +30167,12 @@
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.64), 'mean_duration_us': np.float64(1.7280000000000002), 'median_duration_us': np.float64(1.696), 'std_dev_duration_us': np.float64(0.10516273104099186), 'min_duration_us': np.float64(1.6), 'max_duration_us': np.float64(1.92)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.64, 'mean_duration_us': 1.7280000000000002, 'median_duration_us': 1.696, 'std_dev_duration_us': 0.10516273104099186, 'min_duration_us': 1.6, 'max_duration_us': 1.92}]</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.73)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.73}]</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
@@ -30250,12 +30294,12 @@
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.479), 'mean_duration_us': np.float64(1.6957999999999998), 'median_duration_us': np.float64(1.696), 'std_dev_duration_us': np.float64(0.020556264252047336), 'min_duration_us': np.float64(1.663), 'max_duration_us': np.float64(1.728)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.479, 'mean_duration_us': 1.6957999999999998, 'median_duration_us': 1.696, 'std_dev_duration_us': 0.020556264252047336, 'min_duration_us': 1.663, 'max_duration_us': 1.728}]</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.7)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.7}]</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr"/>
@@ -30373,12 +30417,12 @@
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.447), 'mean_duration_us': np.float64(1.6893999999999998), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.09808486121721335), 'min_duration_us': np.float64(1.599), 'max_duration_us': np.float64(1.824)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.447, 'mean_duration_us': 1.6893999999999998, 'median_duration_us': 1.632, 'std_dev_duration_us': 0.09808486121721335, 'min_duration_us': 1.599, 'max_duration_us': 1.824}]</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ex...', 'stream': 7, 'mean_duration_us': np.float64(1.69)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ex...', 'stream': 7, 'mean_duration_us': 1.69}]</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr"/>
@@ -30526,12 +30570,12 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.030999999999999), 'mean_duration_us': np.float64(1.6061999999999999), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.046786322787754936), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.663)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.030999999999999, 'mean_duration_us': 1.6061999999999999, 'median_duration_us': 1.632, 'std_dev_duration_us': 0.046786322787754936, 'min_duration_us': 1.536, 'max_duration_us': 1.663}]</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.61}]</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
@@ -30679,12 +30723,12 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(7.968), 'mean_duration_us': np.float64(0.7968), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.009600000000000008), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 7.968, 'mean_duration_us': 0.7968, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.009600000000000008, 'min_duration_us': 0.768, 'max_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
@@ -30836,12 +30880,12 @@
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.872), 'mean_duration_us': np.float64(1.5744), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02394660727535325), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.6)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.872, 'mean_duration_us': 1.5744, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02394660727535325, 'min_duration_us': 1.536, 'max_duration_us': 1.6}]</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
@@ -30989,12 +31033,12 @@
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.744), 'mean_duration_us': np.float64(1.5488), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.09185728060420688), 'min_duration_us': np.float64(1.408), 'max_duration_us': np.float64(1.632)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.744, 'mean_duration_us': 1.5488, 'median_duration_us': 1.6, 'std_dev_duration_us': 0.09185728060420688, 'min_duration_us': 1.408, 'max_duration_us': 1.632}]</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.55)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.55}]</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
@@ -31116,12 +31160,12 @@
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.454000000000001), 'mean_duration_us': np.float64(1.4908000000000001), 'median_duration_us': np.float64(1.536), 'std_dev_duration_us': np.float64(0.0797932327957703), 'min_duration_us': np.float64(1.344), 'max_duration_us': np.float64(1.567)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.454000000000001, 'mean_duration_us': 1.4908000000000001, 'median_duration_us': 1.536, 'std_dev_duration_us': 0.0797932327957703, 'min_duration_us': 1.344, 'max_duration_us': 1.567}]</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.49}]</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr"/>
@@ -31269,12 +31313,12 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.424999999999999), 'mean_duration_us': np.float64(1.4849999999999999), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.025502941006872143), 'min_duration_us': np.float64(1.472), 'max_duration_us': np.float64(1.536)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.424999999999999, 'mean_duration_us': 1.4849999999999999, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.025502941006872143, 'min_duration_us': 1.472, 'max_duration_us': 1.536}]</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.48)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.48}]</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
@@ -31426,12 +31470,12 @@
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.264999999999999), 'mean_duration_us': np.float64(1.4529999999999998), 'median_duration_us': np.float64(1.441), 'std_dev_duration_us': np.float64(0.015517731793016656), 'min_duration_us': np.float64(1.44), 'max_duration_us': np.float64(1.472)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.264999999999999, 'mean_duration_us': 1.4529999999999998, 'median_duration_us': 1.441, 'std_dev_duration_us': 0.015517731793016656, 'min_duration_us': 1.44, 'max_duration_us': 1.472}]</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.45)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.45}]</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
@@ -31553,12 +31597,12 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.134), 'mean_duration_us': np.float64(1.4268), 'median_duration_us': np.float64(1.375), 'std_dev_duration_us': np.float64(0.08990083425641834), 'min_duration_us': np.float64(1.343), 'max_duration_us': np.float64(1.536)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.134, 'mean_duration_us': 1.4268, 'median_duration_us': 1.375, 'std_dev_duration_us': 0.08990083425641834, 'min_duration_us': 1.343, 'max_duration_us': 1.536}]</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(1.43)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': 1.43}]</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr"/>
@@ -31676,12 +31720,12 @@
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.103999999999999), 'mean_duration_us': np.float64(1.4207999999999998), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.16639999999999996), 'min_duration_us': np.float64(1.248), 'max_duration_us': np.float64(1.696)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': 7.103999999999999, 'mean_duration_us': 1.4207999999999998, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.16639999999999996, 'min_duration_us': 1.248, 'max_duration_us': 1.696}]</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.42)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': 1.42}]</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr"/>
@@ -31799,12 +31843,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.040000000000001), 'mean_duration_us': np.float64(1.4080000000000001), 'median_duration_us': np.float64(1.344), 'std_dev_duration_us': np.float64(0.09706080568385983), 'min_duration_us': np.float64(1.312), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.040000000000001, 'mean_duration_us': 1.4080000000000001, 'median_duration_us': 1.344, 'std_dev_duration_us': 0.09706080568385983, 'min_duration_us': 1.312, 'max_duration_us': 1.568}]</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.41)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.41}]</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr"/>
@@ -31952,12 +31996,12 @@
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.008999999999999), 'mean_duration_us': np.float64(1.4017999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08894132897590411), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.008999999999999, 'mean_duration_us': 1.4017999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08894132897590411, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
@@ -32079,12 +32123,12 @@
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.008000000000001), 'mean_duration_us': np.float64(1.4016000000000002), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.09997119585160516), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.008000000000001, 'mean_duration_us': 1.4016000000000002, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.09997119585160516, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr"/>
@@ -32232,12 +32276,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.007999999999999), 'mean_duration_us': np.float64(1.4015999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08914168497397834), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.007999999999999, 'mean_duration_us': 1.4015999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08914168497397834, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
@@ -32389,12 +32433,12 @@
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(6.687999999999999), 'mean_duration_us': np.float64(1.3375999999999997), 'median_duration_us': np.float64(1.408), 'std_dev_duration_us': np.float64(0.0868138237840034), 'min_duration_us': np.float64(1.216), 'max_duration_us': np.float64(1.408)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 6.687999999999999, 'mean_duration_us': 1.3375999999999997, 'median_duration_us': 1.408, 'std_dev_duration_us': 0.0868138237840034, 'min_duration_us': 1.216, 'max_duration_us': 1.408}]</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.34)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.34}]</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
@@ -32516,12 +32560,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(6.176), 'mean_duration_us': np.float64(1.2352), 'median_duration_us': np.float64(1.28), 'std_dev_duration_us': np.float64(0.08245823185104081), 'min_duration_us': np.float64(1.12), 'max_duration_us': np.float64(1.312)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 5, 'total_duration_us': 6.176, 'mean_duration_us': 1.2352, 'median_duration_us': 1.28, 'std_dev_duration_us': 0.08245823185104081, 'min_duration_us': 1.12, 'max_duration_us': 1.312}]</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.24)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': 1.24}]</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr"/>
@@ -32639,12 +32683,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(5.984000000000001), 'mean_duration_us': np.float64(1.1968), 'median_duration_us': np.float64(1.12), 'std_dev_duration_us': np.float64(0.09406040612287402), 'min_duration_us': np.float64(1.12), 'max_duration_us': np.float64(1.312)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 5.984000000000001, 'mean_duration_us': 1.1968, 'median_duration_us': 1.12, 'std_dev_duration_us': 0.09406040612287402, 'min_duration_us': 1.12, 'max_duration_us': 1.312}]</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': np.float64(1.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 7, 'mean_duration_us': 1.2}]</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr"/>
@@ -32673,202 +32717,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: M</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: N</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: K</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: stride_A</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: stride_B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_A_B</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -32981,12 +33025,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(130015.7), 'mean_duration_us': np.float64(1083.4641666666666), 'median_duration_us': np.float64(1082.965), 'std_dev_duration_us': np.float64(3.932529614919927), 'min_duration_us': np.float64(1075.574), 'max_duration_us': np.float64(1096.694)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_256x128_tn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 130015.7, 'mean_duration_us': 1083.4641666666666, 'median_duration_us': 1082.965, 'std_dev_duration_us': 3.932529614919927, 'min_duration_us': 1075.574, 'max_duration_us': 1096.694}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': np.float64(1083.46)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_25...', 'stream': 7, 'mean_duration_us': 1083.46}]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -33141,12 +33185,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(99311.41), 'mean_duration_us': np.float64(827.5950833333334), 'median_duration_us': np.float64(826.9205), 'std_dev_duration_us': np.float64(2.9474507419783706), 'min_duration_us': np.float64(825.432), 'max_duration_us': np.float64(851.8)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 120, 'total_duration_us': 99311.41, 'mean_duration_us': 827.5950833333334, 'median_duration_us': 826.9205, 'std_dev_duration_us': 2.9474507419783706, 'min_duration_us': 825.432, 'max_duration_us': 851.8}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': np.float64(827.6)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_12...', 'stream': 7, 'mean_duration_us': 827.6}]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -33301,12 +33345,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(449.6640000000001), 'mean_duration_us': np.float64(0.9368000000000002), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.14700191892171566), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.408)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': np.float64(10035.521), 'mean_duration_us': np.float64(20.90733541666667), 'median_duration_us': np.float64(20.912), 'std_dev_duration_us': np.float64(0.2994497001373127), 'min_duration_us': np.float64(20.256), 'max_duration_us': np.float64(22.015)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 480, 'total_duration_us': 449.6640000000001, 'mean_duration_us': 0.9368000000000002, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.14700191892171566, 'min_duration_us': 0.767, 'max_duration_us': 1.408}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 480, 'total_duration_us': 10035.521, 'mean_duration_us': 20.90733541666667, 'median_duration_us': 20.912, 'std_dev_duration_us': 0.2994497001373127, 'min_duration_us': 20.256, 'max_duration_us': 22.015}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.94)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.91)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.94}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.91}]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -33461,12 +33505,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(115.61200000000002), 'mean_duration_us': np.float64(0.9634333333333335), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.18370559478566667), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.6)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(7766.737), 'mean_duration_us': np.float64(64.72280833333333), 'median_duration_us': np.float64(64.639), 'std_dev_duration_us': np.float64(0.5570301951096441), 'min_duration_us': np.float64(63.711), 'max_duration_us': np.float64(65.951)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 115.61200000000002, 'mean_duration_us': 0.9634333333333335, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.18370559478566667, 'min_duration_us': 0.768, 'max_duration_us': 1.6}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 7766.737, 'mean_duration_us': 64.72280833333333, 'median_duration_us': 64.639, 'std_dev_duration_us': 0.5570301951096441, 'min_duration_us': 63.711, 'max_duration_us': 65.951}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.96)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(64.72)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.96}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 64.72}]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -33621,12 +33665,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(116.09), 'mean_duration_us': np.float64(0.9674166666666667), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.15527371441711854), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.568)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(6884.5689999999995), 'mean_duration_us': np.float64(57.37140833333333), 'median_duration_us': np.float64(57.344), 'std_dev_duration_us': np.float64(0.31250691981227396), 'min_duration_us': np.float64(56.639), 'max_duration_us': np.float64(58.048)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 120, 'total_duration_us': 116.09, 'mean_duration_us': 0.9674166666666667, 'median_duration_us': 0.96, 'std_dev_duration_us': 0.15527371441711854, 'min_duration_us': 0.768, 'max_duration_us': 1.568}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 120, 'total_duration_us': 6884.5689999999995, 'mean_duration_us': 57.37140833333333, 'median_duration_us': 57.344, 'std_dev_duration_us': 0.31250691981227396, 'min_duration_us': 56.639, 'max_duration_us': 58.048}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.97)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(57.37)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.97}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 57.37}]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -33781,12 +33825,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': np.float64(1579.851), 'mean_duration_us': np.float64(6.5827125), 'median_duration_us': np.float64(6.592), 'std_dev_duration_us': np.float64(0.13116311667951205), 'min_duration_us': np.float64(6.303), 'max_duration_us': np.float64(6.975)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 240, 'total_duration_us': 1579.851, 'mean_duration_us': 6.5827125, 'median_duration_us': 6.592, 'std_dev_duration_us': 0.13116311667951205, 'min_duration_us': 6.303, 'max_duration_us': 6.975}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.58)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.58}]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -33941,12 +33985,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(385.4959999999999), 'mean_duration_us': np.float64(6.424933333333332), 'median_duration_us': np.float64(6.336), 'std_dev_duration_us': np.float64(0.19279919317489072), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(6.912)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(140.35000000000002), 'mean_duration_us': np.float64(2.339166666666667), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.037292164801142315), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.496)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 385.4959999999999, 'mean_duration_us': 6.424933333333332, 'median_duration_us': 6.336, 'std_dev_duration_us': 0.19279919317489072, 'min_duration_us': 6.239, 'max_duration_us': 6.912}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, __nv_bfloat16, float, __nv_bfloat16, true, true, false&gt;(cublasLt::cublasSplitKParams&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, float const*, float const*, __nv_bfloat16 const*, __nv_bfloat16 const*, __nv_bfloat16*, void*, long, float*, int*)', 'stream': 7, 'count': 60, 'total_duration_us': 140.35000000000002, 'mean_duration_us': 2.339166666666667, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.037292164801142315, 'min_duration_us': 2.272, 'max_duration_us': 2.496}]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.42)}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 6.42}, {'name': 'void cublasLt::splitKreduce_kernel&lt;32, 16, int, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 2.34}]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -34101,12 +34145,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(17.248), 'mean_duration_us': np.float64(0.8624), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.13365305832639968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.248)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': np.float64(414.7149999999999), 'mean_duration_us': np.float64(20.735749999999996), 'median_duration_us': np.float64(20.768), 'std_dev_duration_us': np.float64(0.42032010123238245), 'min_duration_us': np.float64(19.936), 'max_duration_us': np.float64(21.279)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 20, 'total_duration_us': 17.248, 'mean_duration_us': 0.8624, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.13365305832639968, 'min_duration_us': 0.768, 'max_duration_us': 1.248}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 20, 'total_duration_us': 414.7149999999999, 'mean_duration_us': 20.735749999999996, 'median_duration_us': 20.768, 'std_dev_duration_us': 0.42032010123238245, 'min_duration_us': 19.936, 'max_duration_us': 21.279}]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.86)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(20.74)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 0.86}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': 20.74}]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -34261,12 +34305,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(422.845), 'mean_duration_us': np.float64(7.047416666666667), 'median_duration_us': np.float64(6.976), 'std_dev_duration_us': np.float64(0.17790056133194818), 'min_duration_us': np.float64(6.752), 'max_duration_us': np.float64(7.52)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 422.845, 'mean_duration_us': 7.047416666666667, 'median_duration_us': 6.976, 'std_dev_duration_us': 0.17790056133194818, 'min_duration_us': 6.752, 'max_duration_us': 7.52}]</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(7.05)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': 7.05}]</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -34421,12 +34465,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(185.69699999999997), 'mean_duration_us': np.float64(3.0949499999999994), 'median_duration_us': np.float64(3.104), 'std_dev_duration_us': np.float64(0.04453478977159322), 'min_duration_us': np.float64(3.008), 'max_duration_us': np.float64(3.168)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_tn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 185.69699999999997, 'mean_duration_us': 3.0949499999999994, 'median_duration_us': 3.104, 'std_dev_duration_us': 0.04453478977159322, 'min_duration_us': 3.008, 'max_duration_us': 3.168}]</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(3.09)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 3.09}]</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -34581,12 +34625,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(167.428), 'mean_duration_us': np.float64(2.7904666666666667), 'median_duration_us': np.float64(2.816), 'std_dev_duration_us': np.float64(0.037250264726874344), 'min_duration_us': np.float64(2.72), 'max_duration_us': np.float64(2.88)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1&gt;(cutlass_75_wmma_tensorop_bf16_s161616gemm_bf16_32x32_32x1_nn_align1::Params)', 'stream': 7, 'count': 60, 'total_duration_us': 167.428, 'mean_duration_us': 2.7904666666666667, 'median_duration_us': 2.816, 'std_dev_duration_us': 0.037250264726874344, 'min_duration_us': 2.72, 'max_duration_us': 2.88}]</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(2.79)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 2.79}]</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -34741,12 +34785,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(35.168), 'mean_duration_us': np.float64(2.344533333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.10418372660300108), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.56)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': np.float64(83.104), 'mean_duration_us': np.float64(5.540266666666667), 'median_duration_us': np.float64(5.376), 'std_dev_duration_us': np.float64(0.32818683025916123), 'min_duration_us': np.float64(5.152), 'max_duration_us': np.float64(6.176)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 15, 'total_duration_us': 35.168, 'mean_duration_us': 2.344533333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.10418372660300108, 'min_duration_us': 2.176, 'max_duration_us': 2.56}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 15, 'total_duration_us': 83.104, 'mean_duration_us': 5.540266666666667, 'median_duration_us': 5.376, 'std_dev_duration_us': 0.32818683025916123, 'min_duration_us': 5.152, 'max_duration_us': 6.176}]</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.34)}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(5.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.34}, {'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 5.54}]</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -34901,12 +34945,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(86.78200000000001), 'mean_duration_us': np.float64(17.3564), 'median_duration_us': np.float64(17.376), 'std_dev_duration_us': np.float64(0.07209049868047837), 'min_duration_us': np.float64(17.215), 'max_duration_us': np.float64(17.408)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 5, 'total_duration_us': 86.78200000000001, 'mean_duration_us': 17.3564, 'median_duration_us': 17.376, 'std_dev_duration_us': 0.07209049868047837, 'min_duration_us': 17.215, 'max_duration_us': 17.408}]</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(17.36)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': 17.36}]</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -35061,12 +35105,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(56.54299999999999), 'mean_duration_us': np.float64(11.308599999999998), 'median_duration_us': np.float64(11.296), 'std_dev_duration_us': np.float64(0.10403768547983014), 'min_duration_us': np.float64(11.168), 'max_duration_us': np.float64(11.487)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_32x32_128x2_tn_align2::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 56.54299999999999, 'mean_duration_us': 11.308599999999998, 'median_duration_us': 11.296, 'std_dev_duration_us': 0.10403768547983014, 'min_duration_us': 11.168, 'max_duration_us': 11.487}]</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': np.float64(11.31)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_...', 'stream': 7, 'mean_duration_us': 11.31}]</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -35221,12 +35265,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(23.615000000000002), 'mean_duration_us': np.float64(4.723000000000001), 'median_duration_us': np.float64(4.704), 'std_dev_duration_us': np.float64(0.06861486719363401), 'min_duration_us': np.float64(4.64), 'max_duration_us': np.float64(4.831)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, 128, 16, 4, 4, false, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;, float, float)', 'stream': 7, 'count': 5, 'total_duration_us': 23.615000000000002, 'mean_duration_us': 4.723000000000001, 'median_duration_us': 4.704, 'std_dev_duration_us': 0.06861486719363401, 'min_duration_us': 4.64, 'max_duration_us': 4.831}]</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': np.float64(4.72)}]</t>
+          <t>[{'name': 'void gemv2T_kernel_val&lt;int, int, __nv_bfloat16, __nv_bfloat16, _...', 'stream': 7, 'mean_duration_us': 4.72}]</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -35381,12 +35425,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.143), 'mean_duration_us': np.float64(2.0286), 'median_duration_us': np.float64(2.047), 'std_dev_duration_us': np.float64(0.02545270123189289), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.048)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.183000000000002), 'mean_duration_us': np.float64(2.6366000000000005), 'median_duration_us': np.float64(2.688), 'std_dev_duration_us': np.float64(0.08984341934721768), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt; &gt;(cublasDotParams&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;float&gt; &gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 10.143, 'mean_duration_us': 2.0286, 'median_duration_us': 2.047, 'std_dev_duration_us': 0.02545270123189289, 'min_duration_us': 1.984, 'max_duration_us': 2.048}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStridedBatched&lt;float&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt; &gt;(float const*, float, cublasGemvTensorStridedBatched&lt;float&gt;, int, float const*, float, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, cublasPointerMode_t, cublasLtEpilogue_t, cublasGemvTensorStridedBatched&lt;biasType&lt;cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;::value_type, float&gt;::type const&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.183000000000002, 'mean_duration_us': 2.6366000000000005, 'median_duration_us': 2.688, 'std_dev_duration_us': 0.08984341934721768, 'min_duration_us': 2.527, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': np.float64(2.03)}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': np.float64(2.64)}]</t>
+          <t>[{'name': 'void dot_kernel&lt;float, 128, 0, cublasDotParams&lt;cublasGemvTensorS...', 'stream': 7, 'mean_duration_us': 2.03}, {'name': 'void reduce_1Block_kernel&lt;float, 128, 7, cublasGemvTensorStrided...', 'stream': 7, 'mean_duration_us': 2.64}]</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -35541,12 +35585,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(18.784), 'mean_duration_us': np.float64(3.7567999999999997), 'median_duration_us': np.float64(3.744), 'std_dev_duration_us': np.float64(0.03263372488699366), 'min_duration_us': np.float64(3.712), 'max_duration_us': np.float64(3.808)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 18.784, 'mean_duration_us': 3.7567999999999997, 'median_duration_us': 3.744, 'std_dev_duration_us': 0.03263372488699366, 'min_duration_us': 3.712, 'max_duration_us': 3.808}]</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.76)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.76}]</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -35701,12 +35745,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(17.918), 'mean_duration_us': np.float64(3.5835999999999997), 'median_duration_us': np.float64(3.552), 'std_dev_duration_us': np.float64(0.049834124854360604), 'min_duration_us': np.float64(3.551), 'max_duration_us': np.float64(3.68)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 17.918, 'mean_duration_us': 3.5835999999999997, 'median_duration_us': 3.552, 'std_dev_duration_us': 0.049834124854360604, 'min_duration_us': 3.551, 'max_duration_us': 3.68}]</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int...', 'stream': 7, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -35769,227 +35813,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: convNd</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: input_shape</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: filter_shape</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_input_weight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: input_stride</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: weight_stride</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: stride</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>param: padding</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>param: dilation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>param: transposed_conv</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>param: output_padding</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>param: groups</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -36127,12 +36171,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(28.127000000000002), 'mean_duration_us': np.float64(5.625400000000001), 'median_duration_us': np.float64(5.664), 'std_dev_duration_us': np.float64(0.08941498755801505), 'min_duration_us': np.float64(5.503), 'max_duration_us': np.float64(5.728)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(222.207), 'mean_duration_us': np.float64(44.4414), 'median_duration_us': np.float64(44.384), 'std_dev_duration_us': np.float64(0.1792647204555328), 'min_duration_us': np.float64(44.224), 'max_duration_us': np.float64(44.768)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(10.85), 'mean_duration_us': np.float64(2.17), 'median_duration_us': np.float64(2.176), 'std_dev_duration_us': np.float64(0.013007690033207267), 'min_duration_us': np.float64(2.144), 'max_duration_us': np.float64(2.177)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(58.303000000000004), 'mean_duration_us': np.float64(11.6606), 'median_duration_us': np.float64(11.679), 'std_dev_duration_us': np.float64(0.15088485676170435), 'min_duration_us': np.float64(11.424), 'max_duration_us': np.float64(11.872)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(982.9660000000001), 'mean_duration_us': np.float64(196.59320000000002), 'median_duration_us': np.float64(196.542), 'std_dev_duration_us': np.float64(0.4292092263686784), 'min_duration_us': np.float64(195.966), 'max_duration_us': np.float64(197.245)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(48.35), 'mean_duration_us': np.float64(9.67), 'median_duration_us': np.float64(9.663), 'std_dev_duration_us': np.float64(0.0547539952880155), 'min_duration_us': np.float64(9.6), 'max_duration_us': np.float64(9.759)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 28.127000000000002, 'mean_duration_us': 5.625400000000001, 'median_duration_us': 5.664, 'std_dev_duration_us': 0.08941498755801505, 'min_duration_us': 5.503, 'max_duration_us': 5.728}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 222.207, 'mean_duration_us': 44.4414, 'median_duration_us': 44.384, 'std_dev_duration_us': 0.1792647204555328, 'min_duration_us': 44.224, 'max_duration_us': 44.768}, {'name': 'Memset (Device)', 'stream': 7, 'count': 5, 'total_duration_us': 10.85, 'mean_duration_us': 2.17, 'median_duration_us': 2.176, 'std_dev_duration_us': 0.013007690033207267, 'min_duration_us': 2.144, 'max_duration_us': 2.177}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 58.303000000000004, 'mean_duration_us': 11.6606, 'median_duration_us': 11.679, 'std_dev_duration_us': 0.15088485676170435, 'min_duration_us': 11.424, 'max_duration_us': 11.872}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 5, 'total_duration_us': 982.9660000000001, 'mean_duration_us': 196.59320000000002, 'median_duration_us': 196.542, 'std_dev_duration_us': 0.4292092263686784, 'min_duration_us': 195.966, 'max_duration_us': 197.245}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 5, 'total_duration_us': 48.35, 'mean_duration_us': 9.67, 'median_duration_us': 9.663, 'std_dev_duration_us': 0.0547539952880155, 'min_duration_us': 9.6, 'max_duration_us': 9.759}]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(5.63)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(44.44)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.17)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(11.66)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(196.59)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(9.67)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 5.63}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 44.44}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': 2.17}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 11.66}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': 196.59}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': 9.67}]</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -36195,192 +36239,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: shape_in1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: shape_in2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -36417,7 +36461,11 @@
           <t>(21237760, 4096, 1)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>0.02123776</v>
       </c>
@@ -36479,12 +36527,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(5223.73), 'mean_duration_us': np.float64(43.53108333333333), 'median_duration_us': np.float64(43.3595), 'std_dev_duration_us': np.float64(0.6410638629566389), 'min_duration_us': np.float64(42.656), 'max_duration_us': np.float64(44.704)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 5223.73, 'mean_duration_us': 43.53108333333333, 'median_duration_us': 43.3595, 'std_dev_duration_us': 0.6410638629566389, 'min_duration_us': 42.656, 'max_duration_us': 44.704}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(43.53)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 43.53}]</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -36563,7 +36611,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>0.02123776</v>
       </c>
@@ -36625,12 +36677,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3687.3240000000005), 'mean_duration_us': np.float64(30.727700000000006), 'median_duration_us': np.float64(30.591), 'std_dev_duration_us': np.float64(0.3214868737600341), 'min_duration_us': np.float64(30.336), 'max_duration_us': np.float64(31.711)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3687.3240000000005, 'mean_duration_us': 30.727700000000006, 'median_duration_us': 30.591, 'std_dev_duration_us': 0.3214868737600341, 'min_duration_us': 30.336, 'max_duration_us': 31.711}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(30.73)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 30.73}]</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -36709,7 +36761,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>0.00530944</v>
       </c>
@@ -36771,12 +36827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': np.float64(2317.353), 'mean_duration_us': np.float64(9.458583673469388), 'median_duration_us': np.float64(9.472), 'std_dev_duration_us': np.float64(0.3348456698101192), 'min_duration_us': np.float64(8.576), 'max_duration_us': np.float64(10.849)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 245, 'total_duration_us': 2317.353, 'mean_duration_us': 9.458583673469388, 'median_duration_us': 9.472, 'std_dev_duration_us': 0.3348456698101192, 'min_duration_us': 8.576, 'max_duration_us': 10.849}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(9.46)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 9.46}]</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -36855,7 +36911,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>0.00530944</v>
       </c>
@@ -36917,12 +36977,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(934.809), 'mean_duration_us': np.float64(7.790075), 'median_duration_us': np.float64(7.776), 'std_dev_duration_us': np.float64(0.06863528763204346), 'min_duration_us': np.float64(7.711), 'max_duration_us': np.float64(8.032)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 934.809, 'mean_duration_us': 7.790075, 'median_duration_us': 7.776, 'std_dev_duration_us': 0.06863528763204346, 'min_duration_us': 7.711, 'max_duration_us': 8.032}]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(7.79)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 7.79}]</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -37001,7 +37061,11 @@
           <t>(25, 25, 5, 1)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>3e-07</v>
       </c>
@@ -37063,12 +37127,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(287.13699999999994), 'mean_duration_us': np.float64(2.392808333333333), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.24387456802740948), 'min_duration_us': np.float64(1.984), 'max_duration_us': np.float64(2.913)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 287.13699999999994, 'mean_duration_us': 2.392808333333333, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.24387456802740948, 'min_duration_us': 1.984, 'max_duration_us': 2.913}]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.39)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.39}]</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -37147,7 +37211,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>3.84e-06</v>
       </c>
@@ -37209,12 +37277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': np.float64(187.747), 'mean_duration_us': np.float64(1.5019760000000002), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.09206636423797784), 'min_duration_us': np.float64(1.344), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 125, 'total_duration_us': 187.747, 'mean_duration_us': 1.5019760000000002, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.09206636423797784, 'min_duration_us': 1.344, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.5}]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -37293,7 +37361,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>1.536e-05</v>
       </c>
@@ -37355,12 +37427,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(94.07899999999998), 'mean_duration_us': np.float64(1.567983333333333), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02925092116308288), 'min_duration_us': np.float64(1.535), 'max_duration_us': np.float64(1.633)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 94.07899999999998, 'mean_duration_us': 1.567983333333333, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02925092116308288, 'min_duration_us': 1.535, 'max_duration_us': 1.633}]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -37439,7 +37511,11 @@
           <t>(15360, 3072, 1)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1.536e-05</v>
       </c>
@@ -37501,12 +37577,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(89.14699999999999), 'mean_duration_us': np.float64(1.4857833333333332), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.016880058912482752), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.535)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 89.14699999999999, 'mean_duration_us': 1.4857833333333332, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.016880058912482752, 'min_duration_us': 1.471, 'max_duration_us': 1.535}]</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.49}]</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -37585,7 +37661,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>3.84e-06</v>
       </c>
@@ -37647,12 +37727,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(86.49500000000002), 'mean_duration_us': np.float64(1.4415833333333337), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.10003121040733015), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 86.49500000000002, 'mean_duration_us': 1.4415833333333337, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.10003121040733015, 'min_duration_us': 1.28, 'max_duration_us': 1.568}]</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.44)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': 1.44}]</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -37731,7 +37811,11 @@
           <t>(5309440, 0, 1)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>0.005308416</v>
       </c>
@@ -37793,12 +37877,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(65.407), 'mean_duration_us': np.float64(13.081399999999999), 'median_duration_us': np.float64(13.088), 'std_dev_duration_us': np.float64(0.058854396607220374), 'min_duration_us': np.float64(13.023), 'max_duration_us': np.float64(13.184)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 65.407, 'mean_duration_us': 13.081399999999999, 'median_duration_us': 13.088, 'std_dev_duration_us': 0.058854396607220374, 'min_duration_us': 13.023, 'max_duration_us': 13.184}]</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.08)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.08}]</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -37877,7 +37961,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>0.003981312</v>
       </c>
@@ -37939,12 +38027,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(57.631), 'mean_duration_us': np.float64(11.5262), 'median_duration_us': np.float64(11.552), 'std_dev_duration_us': np.float64(0.0889413289759043), 'min_duration_us': np.float64(11.392), 'max_duration_us': np.float64(11.616)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 57.631, 'mean_duration_us': 11.5262, 'median_duration_us': 11.552, 'std_dev_duration_us': 0.0889413289759043, 'min_duration_us': 11.392, 'max_duration_us': 11.616}]</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(11.53)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 11.53}]</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -38023,7 +38111,11 @@
           <t>(1, 1)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>7.68e-07</v>
       </c>
@@ -38085,12 +38177,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(26.686999999999998), 'mean_duration_us': np.float64(2.6687), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.20862696374150683), 'min_duration_us': np.float64(2.335), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 10, 'total_duration_us': 26.686999999999998, 'mean_duration_us': 2.6687, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.20862696374150683, 'min_duration_us': 2.335, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -38169,7 +38261,11 @@
           <t>(4, 1)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -38231,12 +38327,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(22.144000000000002), 'mean_duration_us': np.float64(4.428800000000001), 'median_duration_us': np.float64(4.416), 'std_dev_duration_us': np.float64(0.09621309682158638), 'min_duration_us': np.float64(4.32), 'max_duration_us': np.float64(4.608)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, 4, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;, TrivialOffsetCalculator&lt;2, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;2&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 22.144000000000002, 'mean_duration_us': 4.428800000000001, 'median_duration_us': 4.416, 'std_dev_duration_us': 0.09621309682158638, 'min_duration_us': 4.32, 'max_duration_us': 4.608}]</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': np.float64(4.43)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::CUDAFun...', 'stream': 7, 'mean_duration_us': 4.43}]</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -38315,7 +38411,11 @@
           <t>(1, 1, 1)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>7.68e-07</v>
       </c>
@@ -38377,12 +38477,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.560000000000002), 'mean_duration_us': np.float64(2.9120000000000004), 'median_duration_us': np.float64(3.008), 'std_dev_duration_us': np.float64(0.21891368161903446), 'min_duration_us': np.float64(2.656), 'max_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 14.560000000000002, 'mean_duration_us': 2.9120000000000004, 'median_duration_us': 3.008, 'std_dev_duration_us': 0.21891368161903446, 'min_duration_us': 2.656, 'max_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.91)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.91}]</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -38461,7 +38561,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>1e-09</v>
       </c>
@@ -38523,12 +38627,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.799), 'mean_duration_us': np.float64(1.7597999999999998), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.10100376230616363), 'min_duration_us': np.float64(1.632), 'max_duration_us': np.float64(1.888)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.799, 'mean_duration_us': 1.7597999999999998, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.10100376230616363, 'min_duration_us': 1.632, 'max_duration_us': 1.888}]</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.76)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.76}]</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -38607,7 +38711,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38669,12 +38777,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.030999999999999), 'mean_duration_us': np.float64(1.6061999999999999), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.046786322787754936), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.663)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.030999999999999, 'mean_duration_us': 1.6061999999999999, 'median_duration_us': 1.632, 'std_dev_duration_us': 0.046786322787754936, 'min_duration_us': 1.536, 'max_duration_us': 1.663}]</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.61}]</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -38753,7 +38861,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38815,12 +38927,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.872), 'mean_duration_us': np.float64(1.5744), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.02394660727535325), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(1.6)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.872, 'mean_duration_us': 1.5744, 'median_duration_us': 1.568, 'std_dev_duration_us': 0.02394660727535325, 'min_duration_us': 1.536, 'max_duration_us': 1.6}]</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.57}]</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -38899,7 +39011,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5e-09</v>
       </c>
@@ -38957,12 +39073,12 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.744), 'mean_duration_us': np.float64(1.5488), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.09185728060420688), 'min_duration_us': np.float64(1.408), 'max_duration_us': np.float64(1.632)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.744, 'mean_duration_us': 1.5488, 'median_duration_us': 1.6, 'std_dev_duration_us': 0.09185728060420688, 'min_duration_us': 1.408, 'max_duration_us': 1.632}]</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.55)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.55}]</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -39041,7 +39157,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39103,12 +39223,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.424999999999999), 'mean_duration_us': np.float64(1.4849999999999999), 'median_duration_us': np.float64(1.472), 'std_dev_duration_us': np.float64(0.025502941006872143), 'min_duration_us': np.float64(1.472), 'max_duration_us': np.float64(1.536)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.424999999999999, 'mean_duration_us': 1.4849999999999999, 'median_duration_us': 1.472, 'std_dev_duration_us': 0.025502941006872143, 'min_duration_us': 1.472, 'max_duration_us': 1.536}]</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.48)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.48}]</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -39187,7 +39307,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39249,12 +39373,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.264999999999999), 'mean_duration_us': np.float64(1.4529999999999998), 'median_duration_us': np.float64(1.441), 'std_dev_duration_us': np.float64(0.015517731793016656), 'min_duration_us': np.float64(1.44), 'max_duration_us': np.float64(1.472)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.264999999999999, 'mean_duration_us': 1.4529999999999998, 'median_duration_us': 1.441, 'std_dev_duration_us': 0.015517731793016656, 'min_duration_us': 1.44, 'max_duration_us': 1.472}]</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.45)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': 1.45}]</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -39333,7 +39457,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>1e-09</v>
       </c>
@@ -39395,12 +39523,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.007999999999999), 'mean_duration_us': np.float64(1.4015999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08914168497397834), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.007999999999999, 'mean_duration_us': 1.4015999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08914168497397834, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -39479,7 +39607,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39601,7 +39733,11 @@
           <t>(5184, 1)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39723,7 +39859,11 @@
           <t>(4, 4, 1)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -39825,182 +39965,182 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: op_shape</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -40093,12 +40233,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8133.554), 'mean_duration_us': np.float64(1626.7108), 'median_duration_us': np.float64(347.196), 'std_dev_duration_us': np.float64(1579.6924965375256), 'min_duration_us': np.float64(325.565), 'max_duration_us': np.float64(3620.445)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 8133.554, 'mean_duration_us': 1626.7108, 'median_duration_us': 347.196, 'std_dev_duration_us': 1579.6924965375256, 'min_duration_us': 325.565, 'max_duration_us': 3620.445}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(1626.71)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 1626.71}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -40233,12 +40373,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': np.float64(5038.033), 'mean_duration_us': np.float64(13.994536111111112), 'median_duration_us': np.float64(13.152), 'std_dev_duration_us': np.float64(1.3500063184322875), 'min_duration_us': np.float64(12.736), 'max_duration_us': np.float64(16.288)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 360, 'total_duration_us': 5038.033, 'mean_duration_us': 13.994536111111112, 'median_duration_us': 13.152, 'std_dev_duration_us': 1.3500063184322875, 'min_duration_us': 12.736, 'max_duration_us': 16.288}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(13.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 13.99}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -40307,7 +40447,11 @@
           <t>(21237760, 4096, 1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>0.02123776</v>
       </c>
@@ -40369,12 +40513,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(3988.498), 'mean_duration_us': np.float64(33.23748333333334), 'median_duration_us': np.float64(33.055), 'std_dev_duration_us': np.float64(0.39268874407375365), 'min_duration_us': np.float64(32.8), 'max_duration_us': np.float64(34.272)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 120, 'total_duration_us': 3988.498, 'mean_duration_us': 33.23748333333334, 'median_duration_us': 33.055, 'std_dev_duration_us': 0.39268874407375365, 'min_duration_us': 32.8, 'max_duration_us': 34.272}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(33.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 33.24}]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -40509,12 +40653,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2338.761), 'mean_duration_us': np.float64(467.7522), 'median_duration_us': np.float64(464.252), 'std_dev_duration_us': np.float64(11.281809454161158), 'min_duration_us': np.float64(454.556), 'max_duration_us': np.float64(487.899)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2338.761, 'mean_duration_us': 467.7522, 'median_duration_us': 464.252, 'std_dev_duration_us': 11.281809454161158, 'min_duration_us': 454.556, 'max_duration_us': 487.899}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(467.75)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 467.75}]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -40649,12 +40793,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(2324.394), 'mean_duration_us': np.float64(464.87879999999996), 'median_duration_us': np.float64(472.188), 'std_dev_duration_us': np.float64(19.601893596282974), 'min_duration_us': np.float64(436.444), 'max_duration_us': np.float64(489.34)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 2324.394, 'mean_duration_us': 464.87879999999996, 'median_duration_us': 472.188, 'std_dev_duration_us': 19.601893596282974, 'min_duration_us': 436.444, 'max_duration_us': 489.34}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(464.88)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 464.88}]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -40789,12 +40933,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': np.float64(1873.8329999999999), 'mean_duration_us': np.float64(15.615274999999999), 'median_duration_us': np.float64(15.584), 'std_dev_duration_us': np.float64(0.1854254999768552), 'min_duration_us': np.float64(15.264), 'max_duration_us': np.float64(16.384)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 120, 'total_duration_us': 1873.8329999999999, 'mean_duration_us': 15.615274999999999, 'median_duration_us': 15.584, 'std_dev_duration_us': 0.1854254999768552, 'min_duration_us': 15.264, 'max_duration_us': 16.384}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(15.62)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 15.62}]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -40929,12 +41073,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(1627.952), 'mean_duration_us': np.float64(325.5904), 'median_duration_us': np.float64(333.501), 'std_dev_duration_us': np.float64(11.368233417730304), 'min_duration_us': np.float64(304.989), 'max_duration_us': np.float64(334.205)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 1627.952, 'mean_duration_us': 325.5904, 'median_duration_us': 333.501, 'std_dev_duration_us': 11.368233417730304, 'min_duration_us': 304.989, 'max_duration_us': 334.205}]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(325.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 325.59}]</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -41069,12 +41213,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': np.float64(457.9199999999999), 'mean_duration_us': np.float64(2.5439999999999996), 'median_duration_us': np.float64(2.4645), 'std_dev_duration_us': np.float64(0.22104903930525865), 'min_duration_us': np.float64(2.24), 'max_duration_us': np.float64(3.232)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 180, 'total_duration_us': 457.9199999999999, 'mean_duration_us': 2.5439999999999996, 'median_duration_us': 2.4645, 'std_dev_duration_us': 0.22104903930525865, 'min_duration_us': 2.24, 'max_duration_us': 3.232}]</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.54)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.54}]</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -41209,12 +41353,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(163.17200000000005), 'mean_duration_us': np.float64(2.719533333333334), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.14011381881250043), 'min_duration_us': np.float64(2.527), 'max_duration_us': np.float64(3.008)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 60, 'total_duration_us': 163.17200000000005, 'mean_duration_us': 2.719533333333334, 'median_duration_us': 2.784, 'std_dev_duration_us': 0.14011381881250043, 'min_duration_us': 2.527, 'max_duration_us': 3.008}]</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -41283,7 +41427,11 @@
           <t>(15360, 3072, 1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>1.536e-05</v>
       </c>
@@ -41345,12 +41493,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': np.float64(105.02100000000002), 'mean_duration_us': np.float64(1.7503500000000003), 'median_duration_us': np.float64(1.76), 'std_dev_duration_us': np.float64(0.021235838418422137), 'min_duration_us': np.float64(1.696), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 60, 'total_duration_us': 105.02100000000002, 'mean_duration_us': 1.7503500000000003, 'median_duration_us': 1.76, 'std_dev_duration_us': 0.021235838418422137, 'min_duration_us': 1.696, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -41485,12 +41633,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(20.255), 'mean_duration_us': np.float64(4.051), 'median_duration_us': np.float64(4.032), 'std_dev_duration_us': np.float64(0.02550294100687212), 'min_duration_us': np.float64(4.032), 'max_duration_us': np.float64(4.096)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 20.255, 'mean_duration_us': 4.051, 'median_duration_us': 4.032, 'std_dev_duration_us': 0.02550294100687212, 'min_duration_us': 4.032, 'max_duration_us': 4.096}]</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(4.05)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 4.05}]</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -41607,12 +41755,12 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(17.44), 'mean_duration_us': np.float64(1.7440000000000002), 'median_duration_us': np.float64(1.7440000000000002), 'std_dev_duration_us': np.float64(0.9569284194755635), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(2.72)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 17.44, 'mean_duration_us': 1.7440000000000002, 'median_duration_us': 1.7440000000000002, 'std_dev_duration_us': 0.9569284194755635, 'min_duration_us': 0.768, 'max_duration_us': 2.72}]</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.74)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.74}]</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -41747,12 +41895,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.717999999999998), 'mean_duration_us': np.float64(2.9435999999999996), 'median_duration_us': np.float64(2.944), 'std_dev_duration_us': np.float64(0.0004898979485565817), 'min_duration_us': np.float64(2.943), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.717999999999998, 'mean_duration_us': 2.9435999999999996, 'median_duration_us': 2.944, 'std_dev_duration_us': 0.0004898979485565817, 'min_duration_us': 2.943, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.94)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.94}]</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -41887,12 +42035,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(14.495999999999999), 'mean_duration_us': np.float64(2.8991999999999996), 'median_duration_us': np.float64(2.912), 'std_dev_duration_us': np.float64(0.032633724886993856), 'min_duration_us': np.float64(2.848), 'max_duration_us': np.float64(2.944)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 14.495999999999999, 'mean_duration_us': 2.8991999999999996, 'median_duration_us': 2.912, 'std_dev_duration_us': 0.032633724886993856, 'min_duration_us': 2.848, 'max_duration_us': 2.944}]</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.9)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.9}]</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -42027,12 +42175,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.985), 'mean_duration_us': np.float64(2.7969999999999997), 'median_duration_us': np.float64(2.785), 'std_dev_duration_us': np.float64(0.015517731793016621), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 13.985, 'mean_duration_us': 2.7969999999999997, 'median_duration_us': 2.785, 'std_dev_duration_us': 0.015517731793016621, 'min_duration_us': 2.784, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.8)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 2.8}]</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -42167,12 +42315,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.472000000000001), 'mean_duration_us': np.float64(2.6944000000000004), 'median_duration_us': np.float64(2.752), 'std_dev_duration_us': np.float64(0.10398769157934018), 'min_duration_us': np.float64(2.528), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.472000000000001, 'mean_duration_us': 2.6944000000000004, 'median_duration_us': 2.752, 'std_dev_duration_us': 0.10398769157934018, 'min_duration_us': 2.528, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.69)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.69}]</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -42307,12 +42455,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.407000000000002), 'mean_duration_us': np.float64(2.6814000000000004), 'median_duration_us': np.float64(2.656), 'std_dev_duration_us': np.float64(0.07142996570067763), 'min_duration_us': np.float64(2.623), 'max_duration_us': np.float64(2.816)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.407000000000002, 'mean_duration_us': 2.6814000000000004, 'median_duration_us': 2.656, 'std_dev_duration_us': 0.07142996570067763, 'min_duration_us': 2.623, 'max_duration_us': 2.816}]</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.68)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.68}]</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -42447,12 +42595,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(13.345), 'mean_duration_us': np.float64(2.669), 'median_duration_us': np.float64(2.72), 'std_dev_duration_us': np.float64(0.08978641322605552), 'min_duration_us': np.float64(2.56), 'max_duration_us': np.float64(2.753)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 13.345, 'mean_duration_us': 2.669, 'median_duration_us': 2.72, 'std_dev_duration_us': 0.08978641322605552, 'min_duration_us': 2.56, 'max_duration_us': 2.753}]</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.67)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.67}]</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -42587,12 +42735,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(12.222999999999999), 'mean_duration_us': np.float64(2.4446), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.1469742834648294), 'min_duration_us': np.float64(2.303), 'max_duration_us': np.float64(2.624)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 5, 'total_duration_us': 12.222999999999999, 'mean_duration_us': 2.4446, 'median_duration_us': 2.336, 'std_dev_duration_us': 0.1469742834648294, 'min_duration_us': 2.303, 'max_duration_us': 2.624}]</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(2.44)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': 2.44}]</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -42727,12 +42875,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.04340691189200176), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.04340691189200176, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -42867,12 +43015,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(11.904), 'mean_duration_us': np.float64(2.3808), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0478932145507065), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.464)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 5, 'total_duration_us': 11.904, 'mean_duration_us': 2.3808, 'median_duration_us': 2.368, 'std_dev_duration_us': 0.0478932145507065, 'min_duration_us': 2.336, 'max_duration_us': 2.464}]</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.38)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': 2.38}]</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -42941,7 +43089,11 @@
           <t>(20736, 4, 1)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F23" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -43003,12 +43155,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.896), 'mean_duration_us': np.float64(1.7792000000000001), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.025600000000000022), 'min_duration_us': np.float64(1.728), 'max_duration_us': np.float64(1.792)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.896, 'mean_duration_us': 1.7792000000000001, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.025600000000000022, 'min_duration_us': 1.728, 'max_duration_us': 1.792}]</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(1.78)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': 1.78}]</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -43125,12 +43277,12 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.769), 'mean_duration_us': np.float64(1.7538), 'median_duration_us': np.float64(1.792), 'std_dev_duration_us': np.float64(0.0742762411542211), 'min_duration_us': np.float64(1.664), 'max_duration_us': np.float64(1.825)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.769, 'mean_duration_us': 1.7538, 'median_duration_us': 1.792, 'std_dev_duration_us': 0.0742762411542211, 'min_duration_us': 1.664, 'max_duration_us': 1.825}]</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.75)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.75}]</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -43247,12 +43399,12 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(8.64), 'mean_duration_us': np.float64(1.7280000000000002), 'median_duration_us': np.float64(1.696), 'std_dev_duration_us': np.float64(0.10516273104099186), 'min_duration_us': np.float64(1.6), 'max_duration_us': np.float64(1.92)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 8.64, 'mean_duration_us': 1.7280000000000002, 'median_duration_us': 1.696, 'std_dev_duration_us': 0.10516273104099186, 'min_duration_us': 1.6, 'max_duration_us': 1.92}]</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(1.73)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': 1.73}]</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -43383,12 +43535,12 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': np.float64(7.968), 'mean_duration_us': np.float64(0.7968), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.009600000000000008), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 10, 'total_duration_us': 7.968, 'mean_duration_us': 0.7968, 'median_duration_us': 0.8, 'std_dev_duration_us': 0.009600000000000008, 'min_duration_us': 0.768, 'max_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(0.8)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': 0.8}]</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -43523,12 +43675,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(7.008999999999999), 'mean_duration_us': np.float64(1.4017999999999997), 'median_duration_us': np.float64(1.44), 'std_dev_duration_us': np.float64(0.08894132897590411), 'min_duration_us': np.float64(1.28), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 5, 'total_duration_us': 7.008999999999999, 'mean_duration_us': 1.4017999999999997, 'median_duration_us': 1.44, 'std_dev_duration_us': 0.08894132897590411, 'min_duration_us': 1.28, 'max_duration_us': 1.504}]</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': 1.4}]</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -43663,12 +43815,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': np.float64(6.687999999999999), 'mean_duration_us': np.float64(1.3375999999999997), 'median_duration_us': np.float64(1.408), 'std_dev_duration_us': np.float64(0.0868138237840034), 'min_duration_us': np.float64(1.216), 'max_duration_us': np.float64(1.408)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'count': 5, 'total_duration_us': 6.687999999999999, 'mean_duration_us': 1.3375999999999997, 'median_duration_us': 1.408, 'std_dev_duration_us': 0.0868138237840034, 'min_duration_us': 1.216, 'max_duration_us': 1.408}]</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(1.34)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 7, 'mean_duration_us': 1.34}]</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -43853,7 +44005,11 @@
           <t>(5184, 1)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F30" t="n">
         <v>5.184e-06</v>
       </c>
@@ -43965,7 +44121,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F31" t="n">
         <v>1e-09</v>
       </c>
@@ -44189,7 +44349,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F33" t="n">
         <v>1e-09</v>
       </c>
